--- a/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simone\Desktop\Accreditamento CVPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F12C83DB-AB94-4AAD-BC73-F51232A080C6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD670DA3-26F7-4D87-9ED6-A96227AF2ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="600" windowWidth="19440" windowHeight="14880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -21,8 +21,8 @@
     <sheet name="Sheet1" sheetId="5" state="hidden" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Summary!$A$1:$G$15</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$34</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="4" hidden="1">Summary!$A$1:$G$10</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="2" hidden="1">TestCases!$A$9:$W$31</definedName>
   </definedNames>
   <calcPr calcId="191028"/>
   <extLst>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="418" uniqueCount="201">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="208">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -94,10 +94,6 @@
   </si>
   <si>
     <t>2) Per tutti i casi di test coerenti con la/e tipologia/e di documento utilizzata/e dal software è necessario compilare SEMPRE la colonna APPLICABILITA' con SI o NO</t>
-  </si>
-  <si>
-    <t>3) Nel caso in cui tra le tipologie documentali oggetto di accreditamento per l'applicativo figurino PSS, RAP, RAD, RSA, LDO, LAB, VPS, SING_VACC, CERT_VACC, TPI, LETT_SCREEN, LETT_VACC, CCE  i relativi casi di test con id 476*, 417, 418, 460, 448, 450, 452,454, 456, 457, 458, 471, 479, 491, 506, 521   che recepiscono quanto previsto dal Decreto 07 settembre 2023, devono essere obbligatoriamente eseguiti e compilati (la colonna APPLICABILITA' deve essere valorizzata con SI). 
-*) Il test in questione è da intendersi obbligatorio per gli applicativi che si stanno accreditando per la prima volta per PSS; nel caso di applicativi già accreditati, sarà sufficiente sottomettere il caso di test 478 (Fast Track)</t>
   </si>
   <si>
     <t>4) Se il test è applicabile la colonna APPLICABILITA' deve essere compilata con SI e dovranno essere valorizzate:
@@ -607,9 +603,6 @@
     <t>Versione:</t>
   </si>
   <si>
-    <t>8.3.0</t>
-  </si>
-  <si>
     <t>Validazione</t>
   </si>
   <si>
@@ -706,160 +699,188 @@
     <t>NO</t>
   </si>
   <si>
+    <t>9.0.0</t>
+  </si>
+  <si>
+    <t>TELEV</t>
+  </si>
+  <si>
+    <t>533,534,535,536,537,538,539,540,541,542,543,544,545,546,547,548,549,550</t>
+  </si>
+  <si>
+    <t>REL_CTC</t>
+  </si>
+  <si>
+    <t>553,554,555,556,557,558,559,560,561,562,563,564,565,566,567,568,569,570</t>
+  </si>
+  <si>
+    <t>551, 552</t>
+  </si>
+  <si>
+    <t>531, 532</t>
+  </si>
+  <si>
+    <t>3) Nel caso in cui tra le tipologie documentali oggetto di accreditamento per l'applicativo figurino PSS, RAP, RAD, RSA, LDO, LAB, VPS, SING_VACC, CERT_VACC, TPI, LETT_SCREEN, LETT_VACC, CCE, TELEV , REL_CTC i relativi casi di test con id 476*, 417, 418, 460, 448, 450, 452,454, 456, 457, 458, 471, 479, 491, 506, 521, 531, 551, che recepiscono quanto previsto dal Decreto 07 settembre 2023, devono essere obbligatoriamente eseguiti e compilati (la colonna APPLICABILITA' deve essere valorizzata con SI). 
+*) Il test in questione è da intendersi obbligatorio per gli applicativi che si stanno accreditando per la prima volta per PSS; nel caso di applicativi già accreditati, sarà sufficiente sottomettere il caso di test 478 (Fast Track)</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:09:54Z</t>
+  </si>
+  <si>
+    <t>39702757cddab418e5fe7ac8c1d75f80</t>
+  </si>
+  <si>
+    <t>UNKNOWN_WORKFLOW_ID</t>
+  </si>
+  <si>
+    <t>Errore generico con possibilitÃ  di aprire ticket</t>
+  </si>
+  <si>
+    <t>Si valutano da backoffice le cause dell'errore e si procede con intervento risolutivo. Successivamente il client puÃ² procedere con un nuovo tentantivo di invio del documento</t>
+  </si>
+  <si>
+    <t>Trattandosi di un potenziale errore di configurazione del sistema; serve un intervento tecnico manuale per correggere la configurazione e ripristinare il corretto funzionamento del servizio. Non Ã¨ possibile implementare un meccanismo automatico di retry o di invio manuale da parte dell'operatore; in quanto non essendo un errore transitorio; Ã¨ necessario intervenire sulla configurazione del sistema per risolverlo.</t>
+  </si>
+  <si>
+    <t>Campo valorizzato in modo fisso nel nell'invocazione del servizio</t>
+  </si>
+  <si>
+    <t>Si valutano da backoffice le cause del timeout e si procede con intervento risolutivo. Successivamente il client puÃ² procedere con un nuovo tentantivo di invio del documento</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:09:55Z</t>
+  </si>
+  <si>
+    <t>603b75fa8547fcf792f1beadedcc62f1</t>
+  </si>
+  <si>
+    <t>Si chiede al client di completare correttamente i dati mancanti obbligatori (o errati) e successivamente si puÃ² procedere ad un reinvio.</t>
+  </si>
+  <si>
+    <t>163ae4772447a0e77d149796464ce89a</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.e135ecd10b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:09:56Z</t>
+  </si>
+  <si>
+    <t>2e4980c8d3e814320516b9be0baf2ed5</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.29ef461ea1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>96dc0c142ed75fdfdc3397468d5a9b6c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.67ede4d03e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:09:57Z</t>
+  </si>
+  <si>
+    <t>0e9048efec64209ff40f88ee405b0c76</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.e0ade7d43e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>0e226372d630b7d3f82651b7f2fd84f0</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.f73b7ff4d9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:09:58Z</t>
+  </si>
+  <si>
+    <t>29f42e00adc64e66f3379bfd537dd4e4</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.a324eae800^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>Campo valorizzato in modo fisso nel CDA</t>
+  </si>
+  <si>
+    <t>0d2f7fa83f24c4e516b4012bf6460b66</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.61a0edf737^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:09:59Z</t>
+  </si>
+  <si>
+    <t>f7c262c458e153dd67a2cc2a4d4dda8c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.bd6aef7f3f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>e1ecf46385f94322dd6da587e9ed2346</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.94dedb6589^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:10:00Z</t>
+  </si>
+  <si>
+    <t>e6b8e8505b938952d043a9aa31d74a60</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.f62c0cb56d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>ecd4eab87931f713807544556bb41a43</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b1ccb8d477^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:10:01Z</t>
+  </si>
+  <si>
+    <t>11ddd03d938d38e9526ef023e615a500</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.38606f276c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>47ef248ec4fcb09a146904313149721f</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.ae940dd255^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-03-20T10:10:02Z</t>
+  </si>
+  <si>
+    <t>4da0ddb5ecaf884682eb7eae6e9d2955</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9312649e23^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>75414d9618f747ef2f319b39d2a5cc41</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9935227025^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>subject_application_id: Lepida_CVPI</t>
+  </si>
+  <si>
     <t>subject_application_vendor: Lepida</t>
   </si>
   <si>
-    <t>subject_application_id: Lepida_CVPI</t>
-  </si>
-  <si>
     <t>subject_application_version: 2.1.0</t>
   </si>
   <si>
-    <t>UNKNOWN_WORKFLOW_ID</t>
-  </si>
-  <si>
-    <t>Errore generico con possibilitÃ  di aprire ticket</t>
-  </si>
-  <si>
-    <t>Trattandosi di un potenziale errore di configurazione del sistema; serve un intervento tecnico manuale per correggere la configurazione e ripristinare il corretto funzionamento del servizio. Non Ã¨ possibile implementare un meccanismo automatico di retry o di invio manuale da parte dell'operatore; in quanto non essendo un errore transitorio; Ã¨ necessario intervenire sulla configurazione del sistema per risolverlo.</t>
-  </si>
-  <si>
-    <t>Campo valorizzato in modo fisso nel nell'invocazione del servizio</t>
-  </si>
-  <si>
-    <t>Campo valorizzato in modo fisso nel CDA</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:54Z</t>
-  </si>
-  <si>
-    <t>39702757cddab418e5fe7ac8c1d75f80</t>
-  </si>
-  <si>
-    <t>Si valutano da backoffice le cause dell'errore e si procede con intervento risolutivo. Successivamente il client puÃ² procedere con un nuovo tentantivo di invio del documento</t>
-  </si>
-  <si>
-    <t>Si valutano da backoffice le cause del timeout e si procede con intervento risolutivo. Successivamente il client puÃ² procedere con un nuovo tentantivo di invio del documento</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:55Z</t>
-  </si>
-  <si>
-    <t>603b75fa8547fcf792f1beadedcc62f1</t>
-  </si>
-  <si>
-    <t>Si chiede al client di completare correttamente i dati mancanti obbligatori (o errati) e successivamente si puÃ² procedere ad un reinvio.</t>
-  </si>
-  <si>
-    <t>163ae4772447a0e77d149796464ce89a</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.e135ecd10b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:56Z</t>
-  </si>
-  <si>
-    <t>2e4980c8d3e814320516b9be0baf2ed5</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.29ef461ea1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>96dc0c142ed75fdfdc3397468d5a9b6c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.67ede4d03e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:57Z</t>
-  </si>
-  <si>
-    <t>0e9048efec64209ff40f88ee405b0c76</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.e0ade7d43e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>0e226372d630b7d3f82651b7f2fd84f0</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.f73b7ff4d9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:58Z</t>
-  </si>
-  <si>
-    <t>29f42e00adc64e66f3379bfd537dd4e4</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.a324eae800^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>0d2f7fa83f24c4e516b4012bf6460b66</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.61a0edf737^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:59Z</t>
-  </si>
-  <si>
-    <t>f7c262c458e153dd67a2cc2a4d4dda8c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.bd6aef7f3f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>e1ecf46385f94322dd6da587e9ed2346</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.94dedb6589^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:10:00Z</t>
-  </si>
-  <si>
-    <t>e6b8e8505b938952d043a9aa31d74a60</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.f62c0cb56d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>ecd4eab87931f713807544556bb41a43</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b1ccb8d477^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:10:01Z</t>
-  </si>
-  <si>
-    <t>11ddd03d938d38e9526ef023e615a500</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.38606f276c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>47ef248ec4fcb09a146904313149721f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.ae940dd255^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:10:02Z</t>
-  </si>
-  <si>
-    <t>4da0ddb5ecaf884682eb7eae6e9d2955</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9312649e23^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>75414d9618f747ef2f319b39d2a5cc41</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9935227025^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>Lepida</t>
   </si>
 </sst>
 </file>
@@ -1001,7 +1022,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="25">
+  <borders count="28">
     <border>
       <left/>
       <right/>
@@ -1298,25 +1319,74 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
       <right/>
-      <top style="medium">
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF000000"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF000000"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
       </top>
       <bottom/>
       <diagonal/>
     </border>
     <border>
-      <left style="medium">
+      <left style="thin">
         <color indexed="64"/>
       </left>
-      <right style="medium">
+      <right style="thin">
         <color indexed="64"/>
       </right>
-      <top style="medium">
+      <top style="thin">
         <color indexed="64"/>
       </top>
-      <bottom/>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color indexed="64"/>
+      </left>
+      <right style="thin">
+        <color indexed="64"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF000000"/>
+      </bottom>
       <diagonal/>
     </border>
   </borders>
@@ -1324,7 +1394,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="57">
+  <cellXfs count="61">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -1352,12 +1422,6 @@
     </xf>
     <xf numFmtId="0" fontId="5" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="14" fillId="0" borderId="12" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
@@ -1398,23 +1462,8 @@
     <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="24" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
     </xf>
     <xf numFmtId="164" fontId="4" fillId="0" borderId="13" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
@@ -1445,6 +1494,33 @@
     </xf>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="25" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1" readingOrder="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="26" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="27" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="25" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="23" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="3" fontId="4" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
+    </xf>
+    <xf numFmtId="3" fontId="0" fillId="0" borderId="24" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1549,6 +1625,10 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -1790,23 +1870,23 @@
       </c>
     </row>
     <row r="4" spans="1:1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A4" s="42" t="s">
-        <v>3</v>
+      <c r="A4" s="35" t="s">
+        <v>154</v>
       </c>
     </row>
     <row r="5" spans="1:1" ht="300" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" ht="90" x14ac:dyDescent="0.25">
+      <c r="A6" s="14" t="s">
         <v>4</v>
       </c>
     </row>
-    <row r="6" spans="1:1" ht="90" x14ac:dyDescent="0.25">
-      <c r="A6" s="16" t="s">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
+      <c r="A7" s="14" t="s">
         <v>5</v>
-      </c>
-    </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="16" t="s">
-        <v>6</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
@@ -1814,17 +1894,17 @@
     </row>
     <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="1" t="s">
-        <v>7</v>
+        <v>6</v>
       </c>
     </row>
     <row r="10" spans="1:1" ht="45" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
-        <v>8</v>
+        <v>7</v>
       </c>
     </row>
     <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
-        <v>9</v>
+        <v>8</v>
       </c>
     </row>
     <row r="12" spans="1:1" x14ac:dyDescent="0.25">
@@ -1851,63 +1931,63 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B1" s="3" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="4" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="B3" s="4"/>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="22">
+      <c r="A4" s="20">
         <v>1</v>
       </c>
-      <c r="B4" s="23" t="s">
+      <c r="B4" s="21" t="s">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="22">
+        <v>2</v>
+      </c>
+      <c r="B5" s="23" t="s">
         <v>12</v>
       </c>
     </row>
-    <row r="5" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24">
-        <v>2</v>
-      </c>
-      <c r="B5" s="25" t="s">
+    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="22">
+        <v>3</v>
+      </c>
+      <c r="B6" s="23" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="6" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24">
-        <v>3</v>
-      </c>
-      <c r="B6" s="25" t="s">
+    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A7" s="22">
+        <v>4</v>
+      </c>
+      <c r="B7" s="23" t="s">
         <v>14</v>
       </c>
     </row>
-    <row r="7" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24">
-        <v>4</v>
-      </c>
-      <c r="B7" s="25" t="s">
+    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A8" s="22">
+        <v>5</v>
+      </c>
+      <c r="B8" s="23" t="s">
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:2" ht="30" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="24">
-        <v>5</v>
-      </c>
-      <c r="B8" s="25" t="s">
+    <row r="9" spans="1:2" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="24">
+        <v>6</v>
+      </c>
+      <c r="B9" s="25" t="s">
         <v>16</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="26">
-        <v>6</v>
-      </c>
-      <c r="B9" s="27" t="s">
-        <v>17</v>
       </c>
     </row>
     <row r="10" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -2905,7 +2985,7 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
-  <dimension ref="A1:W542"/>
+  <dimension ref="A1:W499"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11.42578125" customWidth="1"/>
@@ -2945,12 +3025,14 @@
       <c r="W1" s="9"/>
     </row>
     <row r="2" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="47" t="s">
-        <v>18</v>
-      </c>
-      <c r="B2" s="48"/>
-      <c r="C2" s="49"/>
-      <c r="D2" s="48"/>
+      <c r="A2" s="51" t="s">
+        <v>17</v>
+      </c>
+      <c r="B2" s="52"/>
+      <c r="C2" s="53" t="s">
+        <v>207</v>
+      </c>
+      <c r="D2" s="52"/>
       <c r="F2" s="6"/>
       <c r="G2" s="6"/>
       <c r="H2" s="6"/>
@@ -2971,14 +3053,14 @@
       <c r="W2" s="9"/>
     </row>
     <row r="3" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="50" t="s">
-        <v>19</v>
-      </c>
-      <c r="B3" s="51"/>
-      <c r="C3" s="56" t="s">
-        <v>150</v>
-      </c>
-      <c r="D3" s="48"/>
+      <c r="A3" s="54" t="s">
+        <v>18</v>
+      </c>
+      <c r="B3" s="55"/>
+      <c r="C3" s="60" t="s">
+        <v>204</v>
+      </c>
+      <c r="D3" s="52"/>
       <c r="F3" s="6"/>
       <c r="G3" s="6"/>
       <c r="H3" s="6"/>
@@ -2999,12 +3081,12 @@
       <c r="W3" s="9"/>
     </row>
     <row r="4" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="52"/>
-      <c r="B4" s="53"/>
-      <c r="C4" s="56" t="s">
-        <v>149</v>
-      </c>
-      <c r="D4" s="48"/>
+      <c r="A4" s="56"/>
+      <c r="B4" s="57"/>
+      <c r="C4" s="60" t="s">
+        <v>205</v>
+      </c>
+      <c r="D4" s="52"/>
       <c r="E4" s="4"/>
       <c r="F4" s="6"/>
       <c r="G4" s="6"/>
@@ -3026,12 +3108,12 @@
       <c r="W4" s="9"/>
     </row>
     <row r="5" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="54"/>
-      <c r="B5" s="55"/>
-      <c r="C5" s="56" t="s">
-        <v>151</v>
-      </c>
-      <c r="D5" s="48"/>
+      <c r="A5" s="58"/>
+      <c r="B5" s="59"/>
+      <c r="C5" s="60" t="s">
+        <v>206</v>
+      </c>
+      <c r="D5" s="52"/>
       <c r="F5" s="6"/>
       <c r="G5" s="6"/>
       <c r="H5" s="6"/>
@@ -3052,8 +3134,8 @@
       <c r="W5" s="9"/>
     </row>
     <row r="6" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="45"/>
-      <c r="B6" s="46"/>
+      <c r="A6" s="49"/>
+      <c r="B6" s="50"/>
       <c r="C6" s="10"/>
       <c r="F6" s="6"/>
       <c r="G6" s="6"/>
@@ -3117,1375 +3199,1360 @@
       <c r="V8" s="2"/>
       <c r="W8" s="9"/>
     </row>
-    <row r="9" spans="1:23" s="17" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A9" s="18" t="s">
+    <row r="9" spans="1:23" s="15" customFormat="1" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A9" s="16" t="s">
+        <v>19</v>
+      </c>
+      <c r="B9" s="17" t="s">
         <v>20</v>
       </c>
-      <c r="B9" s="19" t="s">
+      <c r="C9" s="17" t="s">
         <v>21</v>
       </c>
-      <c r="C9" s="19" t="s">
+      <c r="D9" s="17" t="s">
         <v>22</v>
       </c>
-      <c r="D9" s="19" t="s">
+      <c r="E9" s="17" t="s">
         <v>23</v>
       </c>
-      <c r="E9" s="19" t="s">
+      <c r="F9" s="17" t="s">
         <v>24</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="G9" s="17" t="s">
         <v>25</v>
       </c>
-      <c r="G9" s="19" t="s">
+      <c r="H9" s="17" t="s">
         <v>26</v>
       </c>
-      <c r="H9" s="19" t="s">
+      <c r="I9" s="17" t="s">
         <v>27</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="J9" s="17" t="s">
         <v>28</v>
       </c>
-      <c r="J9" s="19" t="s">
+      <c r="K9" s="17" t="s">
         <v>29</v>
       </c>
-      <c r="K9" s="19" t="s">
+      <c r="L9" s="17" t="s">
         <v>30</v>
       </c>
-      <c r="L9" s="19" t="s">
+      <c r="M9" s="17" t="s">
         <v>31</v>
       </c>
-      <c r="M9" s="19" t="s">
+      <c r="N9" s="17" t="s">
         <v>32</v>
       </c>
-      <c r="N9" s="19" t="s">
+      <c r="O9" s="17" t="s">
         <v>33</v>
       </c>
-      <c r="O9" s="19" t="s">
+      <c r="P9" s="17" t="s">
         <v>34</v>
       </c>
-      <c r="P9" s="19" t="s">
+      <c r="Q9" s="17" t="s">
         <v>35</v>
       </c>
-      <c r="Q9" s="19" t="s">
+      <c r="R9" s="17" t="s">
         <v>36</v>
       </c>
-      <c r="R9" s="19" t="s">
+      <c r="S9" s="17" t="s">
         <v>37</v>
       </c>
-      <c r="S9" s="19" t="s">
+      <c r="T9" s="17" t="s">
         <v>38</v>
       </c>
-      <c r="T9" s="19" t="s">
+      <c r="U9" s="18" t="s">
         <v>39</v>
       </c>
-      <c r="U9" s="20" t="s">
+      <c r="V9" s="17" t="s">
         <v>40</v>
       </c>
-      <c r="V9" s="19" t="s">
+      <c r="W9" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="W9" s="21" t="s">
+    </row>
+    <row r="10" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A10" s="27">
+        <v>30</v>
+      </c>
+      <c r="B10" s="27" t="s">
         <v>42</v>
       </c>
-    </row>
-    <row r="10" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A10" s="31"/>
-      <c r="B10" s="31"/>
-      <c r="C10" s="32"/>
-      <c r="D10" s="33"/>
-      <c r="E10" s="41"/>
-      <c r="F10" s="34"/>
-      <c r="G10" s="34"/>
-      <c r="H10" s="34"/>
-      <c r="I10" s="35"/>
-      <c r="J10" s="36"/>
-      <c r="K10" s="36"/>
-      <c r="L10" s="36"/>
-      <c r="M10" s="36"/>
-      <c r="N10" s="36"/>
-      <c r="O10" s="36"/>
-      <c r="P10" s="36"/>
-      <c r="Q10" s="36"/>
-      <c r="R10" s="36"/>
-      <c r="S10" s="36"/>
-      <c r="T10" s="36"/>
-      <c r="U10" s="37"/>
-      <c r="V10" s="38"/>
-      <c r="W10" s="36"/>
+      <c r="C10" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D10" s="27" t="s">
+        <v>49</v>
+      </c>
+      <c r="E10" s="34" t="s">
+        <v>45</v>
+      </c>
+      <c r="F10" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G10" s="28" t="s">
+        <v>155</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>156</v>
+      </c>
+      <c r="I10" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="J10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K10" s="29"/>
+      <c r="L10" s="29"/>
+      <c r="M10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O10" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P10" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q10" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R10" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="S10" s="29" t="s">
+        <v>159</v>
+      </c>
+      <c r="T10" s="29"/>
+      <c r="U10" s="30"/>
+      <c r="V10" s="31" t="s">
+        <v>160</v>
+      </c>
+      <c r="W10" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="11" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A11" s="33"/>
-      <c r="B11" s="33"/>
-      <c r="C11" s="39"/>
-      <c r="D11" s="33"/>
-      <c r="E11" s="41"/>
-      <c r="F11" s="35"/>
-      <c r="G11" s="35"/>
-      <c r="H11" s="35"/>
-      <c r="I11" s="40"/>
-      <c r="J11" s="36"/>
-      <c r="K11" s="36"/>
-      <c r="L11" s="36"/>
-      <c r="M11" s="36"/>
-      <c r="N11" s="36"/>
-      <c r="O11" s="36"/>
-      <c r="P11" s="36"/>
-      <c r="Q11" s="36"/>
-      <c r="R11" s="36"/>
-      <c r="S11" s="36"/>
-      <c r="T11" s="36"/>
-      <c r="U11" s="37"/>
-      <c r="V11" s="38"/>
-      <c r="W11" s="36"/>
+      <c r="A11" s="27">
+        <v>38</v>
+      </c>
+      <c r="B11" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C11" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D11" s="27" t="s">
+        <v>56</v>
+      </c>
+      <c r="E11" s="34" t="s">
+        <v>55</v>
+      </c>
+      <c r="F11" s="28"/>
+      <c r="G11" s="28"/>
+      <c r="H11" s="28"/>
+      <c r="I11" s="33"/>
+      <c r="J11" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="K11" s="29" t="s">
+        <v>161</v>
+      </c>
+      <c r="L11" s="29"/>
+      <c r="M11" s="29"/>
+      <c r="N11" s="29"/>
+      <c r="O11" s="29"/>
+      <c r="P11" s="29"/>
+      <c r="Q11" s="29"/>
+      <c r="R11" s="29"/>
+      <c r="S11" s="29"/>
+      <c r="T11" s="29"/>
+      <c r="U11" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="V11" s="31"/>
+      <c r="W11" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="12" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A12" s="33"/>
-      <c r="B12" s="33"/>
-      <c r="C12" s="39"/>
-      <c r="D12" s="33"/>
-      <c r="E12" s="41"/>
-      <c r="F12" s="35"/>
-      <c r="G12" s="35"/>
-      <c r="H12" s="35"/>
-      <c r="I12" s="40"/>
-      <c r="J12" s="36"/>
-      <c r="K12" s="36"/>
-      <c r="L12" s="36"/>
-      <c r="M12" s="36"/>
-      <c r="N12" s="36"/>
-      <c r="O12" s="36"/>
-      <c r="P12" s="36"/>
-      <c r="Q12" s="36"/>
-      <c r="R12" s="36"/>
-      <c r="S12" s="36"/>
-      <c r="T12" s="36"/>
-      <c r="U12" s="37"/>
-      <c r="V12" s="38"/>
-      <c r="W12" s="36"/>
+      <c r="A12" s="27">
+        <v>46</v>
+      </c>
+      <c r="B12" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C12" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D12" s="27" t="s">
+        <v>59</v>
+      </c>
+      <c r="E12" s="34" t="s">
+        <v>57</v>
+      </c>
+      <c r="F12" s="28"/>
+      <c r="G12" s="28"/>
+      <c r="H12" s="28"/>
+      <c r="I12" s="33"/>
+      <c r="J12" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K12" s="29"/>
+      <c r="L12" s="29"/>
+      <c r="M12" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N12" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O12" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P12" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q12" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R12" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="S12" s="29" t="s">
+        <v>162</v>
+      </c>
+      <c r="T12" s="29"/>
+      <c r="U12" s="30"/>
+      <c r="V12" s="31"/>
+      <c r="W12" s="29" t="s">
+        <v>46</v>
+      </c>
     </row>
     <row r="13" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A13" s="33">
-        <v>30</v>
-      </c>
-      <c r="B13" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C13" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D13" s="33" t="s">
-        <v>50</v>
-      </c>
-      <c r="E13" s="41" t="s">
+      <c r="A13" s="27">
+        <v>175</v>
+      </c>
+      <c r="B13" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C13" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D13" s="27" t="s">
+        <v>60</v>
+      </c>
+      <c r="E13" s="34" t="s">
+        <v>61</v>
+      </c>
+      <c r="F13" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G13" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="H13" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="I13" s="33" t="s">
+        <v>157</v>
+      </c>
+      <c r="J13" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K13" s="29"/>
+      <c r="L13" s="29"/>
+      <c r="M13" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N13" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O13" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P13" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q13" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R13" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S13" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T13" s="29"/>
+      <c r="U13" s="30"/>
+      <c r="V13" s="31"/>
+      <c r="W13" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="F13" s="35">
+    </row>
+    <row r="14" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A14" s="27">
+        <v>177</v>
+      </c>
+      <c r="B14" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C14" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D14" s="27" t="s">
+        <v>62</v>
+      </c>
+      <c r="E14" s="34" t="s">
+        <v>63</v>
+      </c>
+      <c r="F14" s="28">
         <v>46101</v>
       </c>
-      <c r="G13" s="35" t="s">
-        <v>157</v>
-      </c>
-      <c r="H13" s="35" t="s">
+      <c r="G14" s="28" t="s">
+        <v>163</v>
+      </c>
+      <c r="H14" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="I14" s="33" t="s">
+        <v>167</v>
+      </c>
+      <c r="J14" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K14" s="29"/>
+      <c r="L14" s="29"/>
+      <c r="M14" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N14" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O14" s="29" t="s">
         <v>158</v>
       </c>
-      <c r="I13" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="J13" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K13" s="36"/>
-      <c r="L13" s="36"/>
-      <c r="M13" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N13" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O13" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P13" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q13" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R13" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="S13" s="36" t="s">
-        <v>159</v>
-      </c>
-      <c r="T13" s="36"/>
-      <c r="U13" s="37"/>
-      <c r="V13" s="38" t="s">
-        <v>154</v>
-      </c>
-      <c r="W13" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="14" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A14" s="33">
-        <v>38</v>
-      </c>
-      <c r="B14" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C14" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D14" s="33" t="s">
-        <v>57</v>
-      </c>
-      <c r="E14" s="41" t="s">
-        <v>56</v>
-      </c>
-      <c r="F14" s="35"/>
-      <c r="G14" s="35"/>
-      <c r="H14" s="35"/>
-      <c r="I14" s="40"/>
-      <c r="J14" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="K14" s="36" t="s">
-        <v>155</v>
-      </c>
-      <c r="L14" s="36"/>
-      <c r="M14" s="36"/>
-      <c r="N14" s="36"/>
-      <c r="O14" s="36"/>
-      <c r="P14" s="36"/>
-      <c r="Q14" s="36"/>
-      <c r="R14" s="36"/>
-      <c r="S14" s="36"/>
-      <c r="T14" s="36"/>
-      <c r="U14" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="V14" s="38"/>
-      <c r="W14" s="36" t="s">
-        <v>47</v>
+      <c r="P14" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q14" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R14" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S14" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T14" s="29"/>
+      <c r="U14" s="30"/>
+      <c r="V14" s="31"/>
+      <c r="W14" s="29" t="s">
+        <v>46</v>
       </c>
     </row>
     <row r="15" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A15" s="33">
+      <c r="A15" s="27">
+        <v>178</v>
+      </c>
+      <c r="B15" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C15" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D15" s="27" t="s">
+        <v>64</v>
+      </c>
+      <c r="E15" s="34" t="s">
+        <v>65</v>
+      </c>
+      <c r="F15" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G15" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="H15" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="I15" s="33" t="s">
+        <v>170</v>
+      </c>
+      <c r="J15" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K15" s="29"/>
+      <c r="L15" s="29"/>
+      <c r="M15" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N15" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O15" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P15" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q15" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R15" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S15" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T15" s="29"/>
+      <c r="U15" s="30"/>
+      <c r="V15" s="31"/>
+      <c r="W15" s="29" t="s">
         <v>46</v>
       </c>
-      <c r="B15" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C15" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D15" s="33" t="s">
-        <v>60</v>
-      </c>
-      <c r="E15" s="41" t="s">
+    </row>
+    <row r="16" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A16" s="27">
+        <v>179</v>
+      </c>
+      <c r="B16" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C16" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D16" s="27" t="s">
+        <v>66</v>
+      </c>
+      <c r="E16" s="34" t="s">
+        <v>67</v>
+      </c>
+      <c r="F16" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G16" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="H16" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="I16" s="33" t="s">
+        <v>172</v>
+      </c>
+      <c r="J16" s="29" t="s">
         <v>58</v>
       </c>
-      <c r="F15" s="35"/>
-      <c r="G15" s="35"/>
-      <c r="H15" s="35"/>
-      <c r="I15" s="40"/>
-      <c r="J15" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K15" s="36"/>
-      <c r="L15" s="36"/>
-      <c r="M15" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N15" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O15" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P15" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q15" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R15" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="S15" s="36" t="s">
-        <v>160</v>
-      </c>
-      <c r="T15" s="36"/>
-      <c r="U15" s="37"/>
-      <c r="V15" s="38"/>
-      <c r="W15" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="16" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A16" s="33">
+      <c r="K16" s="29"/>
+      <c r="L16" s="29"/>
+      <c r="M16" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N16" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O16" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P16" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q16" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R16" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S16" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T16" s="29"/>
+      <c r="U16" s="30"/>
+      <c r="V16" s="31"/>
+      <c r="W16" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="17" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A17" s="27">
+        <v>180</v>
+      </c>
+      <c r="B17" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C17" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D17" s="27" t="s">
+        <v>68</v>
+      </c>
+      <c r="E17" s="34" t="s">
+        <v>69</v>
+      </c>
+      <c r="F17" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G17" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H17" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="I17" s="33" t="s">
         <v>175</v>
       </c>
-      <c r="B16" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C16" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D16" s="33" t="s">
-        <v>61</v>
-      </c>
-      <c r="E16" s="41" t="s">
-        <v>62</v>
-      </c>
-      <c r="F16" s="35">
+      <c r="J17" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K17" s="29"/>
+      <c r="L17" s="29"/>
+      <c r="M17" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N17" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O17" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P17" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q17" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R17" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S17" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T17" s="29"/>
+      <c r="U17" s="30"/>
+      <c r="V17" s="31"/>
+      <c r="W17" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="18" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A18" s="27">
+        <v>181</v>
+      </c>
+      <c r="B18" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C18" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D18" s="27" t="s">
+        <v>70</v>
+      </c>
+      <c r="E18" s="34" t="s">
+        <v>71</v>
+      </c>
+      <c r="F18" s="28">
         <v>46101</v>
       </c>
-      <c r="G16" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="H16" s="35" t="s">
-        <v>162</v>
-      </c>
-      <c r="I16" s="40" t="s">
-        <v>152</v>
-      </c>
-      <c r="J16" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K16" s="36"/>
-      <c r="L16" s="36"/>
-      <c r="M16" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N16" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O16" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P16" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q16" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R16" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S16" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T16" s="36"/>
-      <c r="U16" s="37"/>
-      <c r="V16" s="38"/>
-      <c r="W16" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="17" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A17" s="33">
+      <c r="G18" s="28" t="s">
+        <v>173</v>
+      </c>
+      <c r="H18" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="I18" s="33" t="s">
         <v>177</v>
       </c>
-      <c r="B17" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C17" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D17" s="33" t="s">
-        <v>63</v>
-      </c>
-      <c r="E17" s="41" t="s">
-        <v>64</v>
-      </c>
-      <c r="F17" s="35">
+      <c r="J18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K18" s="29"/>
+      <c r="L18" s="29"/>
+      <c r="M18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O18" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q18" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R18" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S18" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T18" s="29"/>
+      <c r="U18" s="30"/>
+      <c r="V18" s="31"/>
+      <c r="W18" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="19" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A19" s="27">
+        <v>182</v>
+      </c>
+      <c r="B19" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C19" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D19" s="27" t="s">
+        <v>72</v>
+      </c>
+      <c r="E19" s="34" t="s">
+        <v>73</v>
+      </c>
+      <c r="F19" s="28">
         <v>46101</v>
       </c>
-      <c r="G17" s="35" t="s">
-        <v>161</v>
-      </c>
-      <c r="H17" s="35" t="s">
-        <v>164</v>
-      </c>
-      <c r="I17" s="40" t="s">
+      <c r="G19" s="28" t="s">
+        <v>178</v>
+      </c>
+      <c r="H19" s="28" t="s">
+        <v>179</v>
+      </c>
+      <c r="I19" s="33" t="s">
+        <v>180</v>
+      </c>
+      <c r="J19" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K19" s="29"/>
+      <c r="L19" s="29"/>
+      <c r="M19" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N19" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O19" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P19" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q19" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R19" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S19" s="29" t="s">
         <v>165</v>
       </c>
-      <c r="J17" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K17" s="36"/>
-      <c r="L17" s="36"/>
-      <c r="M17" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N17" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O17" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P17" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q17" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R17" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S17" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T17" s="36"/>
-      <c r="U17" s="37"/>
-      <c r="V17" s="38"/>
-      <c r="W17" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="18" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A18" s="33">
+      <c r="T19" s="29"/>
+      <c r="U19" s="30"/>
+      <c r="V19" s="31"/>
+      <c r="W19" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A20" s="27">
+        <v>183</v>
+      </c>
+      <c r="B20" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C20" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D20" s="27" t="s">
+        <v>74</v>
+      </c>
+      <c r="E20" s="34" t="s">
+        <v>75</v>
+      </c>
+      <c r="F20" s="28"/>
+      <c r="G20" s="28"/>
+      <c r="H20" s="28"/>
+      <c r="I20" s="33"/>
+      <c r="J20" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="K20" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L20" s="29"/>
+      <c r="M20" s="29"/>
+      <c r="N20" s="29"/>
+      <c r="O20" s="29"/>
+      <c r="P20" s="29"/>
+      <c r="Q20" s="29"/>
+      <c r="R20" s="29"/>
+      <c r="S20" s="29"/>
+      <c r="T20" s="29"/>
+      <c r="U20" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="V20" s="31"/>
+      <c r="W20" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="21" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A21" s="27">
+        <v>184</v>
+      </c>
+      <c r="B21" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C21" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D21" s="27" t="s">
+        <v>76</v>
+      </c>
+      <c r="E21" s="34" t="s">
+        <v>77</v>
+      </c>
+      <c r="F21" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G21" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="B18" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C18" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D18" s="33" t="s">
-        <v>65</v>
-      </c>
-      <c r="E18" s="41" t="s">
-        <v>66</v>
-      </c>
-      <c r="F18" s="35">
+      <c r="H21" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="I21" s="33" t="s">
+        <v>183</v>
+      </c>
+      <c r="J21" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K21" s="29"/>
+      <c r="L21" s="29"/>
+      <c r="M21" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N21" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O21" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P21" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q21" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R21" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S21" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T21" s="29"/>
+      <c r="U21" s="30"/>
+      <c r="V21" s="31"/>
+      <c r="W21" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="22" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A22" s="27">
+        <v>185</v>
+      </c>
+      <c r="B22" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C22" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" s="27" t="s">
+        <v>78</v>
+      </c>
+      <c r="E22" s="34" t="s">
+        <v>79</v>
+      </c>
+      <c r="F22" s="28">
         <v>46101</v>
       </c>
-      <c r="G18" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="H18" s="35" t="s">
-        <v>167</v>
-      </c>
-      <c r="I18" s="40" t="s">
-        <v>168</v>
-      </c>
-      <c r="J18" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K18" s="36"/>
-      <c r="L18" s="36"/>
-      <c r="M18" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N18" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O18" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P18" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q18" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R18" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S18" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T18" s="36"/>
-      <c r="U18" s="37"/>
-      <c r="V18" s="38"/>
-      <c r="W18" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="19" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A19" s="33">
-        <v>179</v>
-      </c>
-      <c r="B19" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C19" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D19" s="33" t="s">
-        <v>67</v>
-      </c>
-      <c r="E19" s="41" t="s">
-        <v>68</v>
-      </c>
-      <c r="F19" s="35">
+      <c r="G22" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>185</v>
+      </c>
+      <c r="I22" s="33" t="s">
+        <v>186</v>
+      </c>
+      <c r="J22" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K22" s="29"/>
+      <c r="L22" s="29"/>
+      <c r="M22" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N22" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O22" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P22" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q22" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R22" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S22" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T22" s="29"/>
+      <c r="U22" s="30"/>
+      <c r="V22" s="31"/>
+      <c r="W22" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="23" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A23" s="27">
+        <v>186</v>
+      </c>
+      <c r="B23" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C23" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D23" s="27" t="s">
+        <v>80</v>
+      </c>
+      <c r="E23" s="34" t="s">
+        <v>81</v>
+      </c>
+      <c r="F23" s="28">
         <v>46101</v>
       </c>
-      <c r="G19" s="35" t="s">
-        <v>166</v>
-      </c>
-      <c r="H19" s="35" t="s">
-        <v>169</v>
-      </c>
-      <c r="I19" s="40" t="s">
-        <v>170</v>
-      </c>
-      <c r="J19" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K19" s="36"/>
-      <c r="L19" s="36"/>
-      <c r="M19" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N19" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O19" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P19" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q19" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R19" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S19" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T19" s="36"/>
-      <c r="U19" s="37"/>
-      <c r="V19" s="38"/>
-      <c r="W19" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="20" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A20" s="33">
-        <v>180</v>
-      </c>
-      <c r="B20" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C20" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D20" s="33" t="s">
-        <v>69</v>
-      </c>
-      <c r="E20" s="41" t="s">
-        <v>70</v>
-      </c>
-      <c r="F20" s="35">
+      <c r="G23" s="28" t="s">
+        <v>184</v>
+      </c>
+      <c r="H23" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="I23" s="33" t="s">
+        <v>188</v>
+      </c>
+      <c r="J23" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K23" s="29"/>
+      <c r="L23" s="29"/>
+      <c r="M23" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N23" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O23" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P23" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q23" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R23" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S23" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T23" s="29"/>
+      <c r="U23" s="30"/>
+      <c r="V23" s="31"/>
+      <c r="W23" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="24" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A24" s="27">
+        <v>187</v>
+      </c>
+      <c r="B24" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C24" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D24" s="27" t="s">
+        <v>82</v>
+      </c>
+      <c r="E24" s="34" t="s">
+        <v>83</v>
+      </c>
+      <c r="F24" s="28">
         <v>46101</v>
       </c>
-      <c r="G20" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="H20" s="35" t="s">
-        <v>172</v>
-      </c>
-      <c r="I20" s="40" t="s">
-        <v>173</v>
-      </c>
-      <c r="J20" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K20" s="36"/>
-      <c r="L20" s="36"/>
-      <c r="M20" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N20" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O20" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P20" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q20" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R20" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S20" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T20" s="36"/>
-      <c r="U20" s="37"/>
-      <c r="V20" s="38"/>
-      <c r="W20" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="21" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A21" s="33">
+      <c r="G24" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>190</v>
+      </c>
+      <c r="I24" s="33" t="s">
+        <v>191</v>
+      </c>
+      <c r="J24" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K24" s="29"/>
+      <c r="L24" s="29"/>
+      <c r="M24" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N24" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O24" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P24" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q24" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R24" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S24" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T24" s="29"/>
+      <c r="U24" s="30"/>
+      <c r="V24" s="31"/>
+      <c r="W24" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="25" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A25" s="27">
+        <v>188</v>
+      </c>
+      <c r="B25" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C25" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D25" s="27" t="s">
+        <v>84</v>
+      </c>
+      <c r="E25" s="34" t="s">
+        <v>85</v>
+      </c>
+      <c r="F25" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G25" s="28" t="s">
+        <v>189</v>
+      </c>
+      <c r="H25" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="I25" s="33" t="s">
+        <v>193</v>
+      </c>
+      <c r="J25" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K25" s="29"/>
+      <c r="L25" s="29"/>
+      <c r="M25" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N25" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O25" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P25" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q25" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R25" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S25" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T25" s="29"/>
+      <c r="U25" s="30"/>
+      <c r="V25" s="31"/>
+      <c r="W25" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="26" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A26" s="27">
+        <v>189</v>
+      </c>
+      <c r="B26" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C26" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D26" s="27" t="s">
+        <v>86</v>
+      </c>
+      <c r="E26" s="34" t="s">
+        <v>87</v>
+      </c>
+      <c r="F26" s="28">
+        <v>46101</v>
+      </c>
+      <c r="G26" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>195</v>
+      </c>
+      <c r="I26" s="33" t="s">
+        <v>196</v>
+      </c>
+      <c r="J26" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K26" s="29"/>
+      <c r="L26" s="29"/>
+      <c r="M26" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="N26" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="O26" s="29" t="s">
+        <v>158</v>
+      </c>
+      <c r="P26" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="Q26" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="R26" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="S26" s="29" t="s">
+        <v>165</v>
+      </c>
+      <c r="T26" s="29"/>
+      <c r="U26" s="30"/>
+      <c r="V26" s="31"/>
+      <c r="W26" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="27" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A27" s="27">
+        <v>190</v>
+      </c>
+      <c r="B27" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C27" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D27" s="27" t="s">
+        <v>88</v>
+      </c>
+      <c r="E27" s="34" t="s">
+        <v>89</v>
+      </c>
+      <c r="F27" s="28"/>
+      <c r="G27" s="28"/>
+      <c r="H27" s="28"/>
+      <c r="I27" s="33"/>
+      <c r="J27" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="K27" s="29" t="s">
         <v>181</v>
       </c>
-      <c r="B21" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C21" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D21" s="33" t="s">
-        <v>71</v>
-      </c>
-      <c r="E21" s="41" t="s">
-        <v>72</v>
-      </c>
-      <c r="F21" s="35">
+      <c r="L27" s="29"/>
+      <c r="M27" s="29"/>
+      <c r="N27" s="29"/>
+      <c r="O27" s="29"/>
+      <c r="P27" s="29"/>
+      <c r="Q27" s="29"/>
+      <c r="R27" s="29"/>
+      <c r="S27" s="29"/>
+      <c r="T27" s="29"/>
+      <c r="U27" s="30" t="s">
+        <v>58</v>
+      </c>
+      <c r="V27" s="31"/>
+      <c r="W27" s="29" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="28" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A28" s="27">
+        <v>469</v>
+      </c>
+      <c r="B28" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C28" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D28" s="27" t="s">
+        <v>91</v>
+      </c>
+      <c r="E28" s="34" t="s">
+        <v>92</v>
+      </c>
+      <c r="F28" s="27"/>
+      <c r="G28" s="27"/>
+      <c r="H28" s="27"/>
+      <c r="I28" s="27"/>
+      <c r="J28" s="29" t="s">
+        <v>146</v>
+      </c>
+      <c r="K28" s="29" t="s">
+        <v>181</v>
+      </c>
+      <c r="L28" s="27"/>
+      <c r="M28" s="29"/>
+      <c r="N28" s="29"/>
+      <c r="O28" s="27"/>
+      <c r="P28" s="29"/>
+      <c r="Q28" s="29"/>
+      <c r="R28" s="29"/>
+      <c r="S28" s="27"/>
+      <c r="T28" s="29"/>
+      <c r="U28" s="27" t="s">
+        <v>58</v>
+      </c>
+      <c r="V28" s="27"/>
+      <c r="W28" s="27" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="29" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A29" s="27">
+        <v>476</v>
+      </c>
+      <c r="B29" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C29" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D29" s="27" t="s">
+        <v>93</v>
+      </c>
+      <c r="E29" s="34" t="s">
+        <v>94</v>
+      </c>
+      <c r="F29" s="28">
         <v>46101</v>
       </c>
-      <c r="G21" s="35" t="s">
-        <v>171</v>
-      </c>
-      <c r="H21" s="35" t="s">
-        <v>174</v>
-      </c>
-      <c r="I21" s="40" t="s">
-        <v>175</v>
-      </c>
-      <c r="J21" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K21" s="36"/>
-      <c r="L21" s="36"/>
-      <c r="M21" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N21" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O21" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P21" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q21" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R21" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S21" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T21" s="36"/>
-      <c r="U21" s="37"/>
-      <c r="V21" s="38"/>
-      <c r="W21" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="22" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A22" s="33">
-        <v>182</v>
-      </c>
-      <c r="B22" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C22" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D22" s="33" t="s">
-        <v>73</v>
-      </c>
-      <c r="E22" s="41" t="s">
-        <v>74</v>
-      </c>
-      <c r="F22" s="35">
+      <c r="G29" s="28" t="s">
+        <v>194</v>
+      </c>
+      <c r="H29" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="I29" s="33" t="s">
+        <v>198</v>
+      </c>
+      <c r="J29" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K29" s="29"/>
+      <c r="L29" s="29"/>
+      <c r="M29" s="29"/>
+      <c r="N29" s="29"/>
+      <c r="O29" s="29"/>
+      <c r="P29" s="29"/>
+      <c r="Q29" s="29"/>
+      <c r="R29" s="29"/>
+      <c r="S29" s="29"/>
+      <c r="T29" s="29"/>
+      <c r="U29" s="30"/>
+      <c r="V29" s="31"/>
+      <c r="W29" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="30" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A30" s="27">
+        <v>477</v>
+      </c>
+      <c r="B30" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C30" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D30" s="27" t="s">
+        <v>95</v>
+      </c>
+      <c r="E30" s="34" t="s">
+        <v>96</v>
+      </c>
+      <c r="F30" s="28">
         <v>46101</v>
       </c>
-      <c r="G22" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="H22" s="35" t="s">
-        <v>177</v>
-      </c>
-      <c r="I22" s="40" t="s">
-        <v>178</v>
-      </c>
-      <c r="J22" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K22" s="36"/>
-      <c r="L22" s="36"/>
-      <c r="M22" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N22" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O22" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P22" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q22" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R22" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S22" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T22" s="36"/>
-      <c r="U22" s="37"/>
-      <c r="V22" s="38"/>
-      <c r="W22" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="23" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A23" s="33">
-        <v>183</v>
-      </c>
-      <c r="B23" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C23" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D23" s="33" t="s">
-        <v>75</v>
-      </c>
-      <c r="E23" s="41" t="s">
-        <v>76</v>
-      </c>
-      <c r="F23" s="35"/>
-      <c r="G23" s="35"/>
-      <c r="H23" s="35"/>
-      <c r="I23" s="40"/>
-      <c r="J23" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="K23" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="L23" s="36"/>
-      <c r="M23" s="36"/>
-      <c r="N23" s="36"/>
-      <c r="O23" s="36"/>
-      <c r="P23" s="36"/>
-      <c r="Q23" s="36"/>
-      <c r="R23" s="36"/>
-      <c r="S23" s="36"/>
-      <c r="T23" s="36"/>
-      <c r="U23" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="V23" s="38"/>
-      <c r="W23" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="24" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A24" s="33">
-        <v>184</v>
-      </c>
-      <c r="B24" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C24" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D24" s="33" t="s">
-        <v>77</v>
-      </c>
-      <c r="E24" s="41" t="s">
-        <v>78</v>
-      </c>
-      <c r="F24" s="35">
+      <c r="G30" s="28" t="s">
+        <v>199</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>200</v>
+      </c>
+      <c r="I30" s="33" t="s">
+        <v>201</v>
+      </c>
+      <c r="J30" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K30" s="29"/>
+      <c r="L30" s="29"/>
+      <c r="M30" s="29"/>
+      <c r="N30" s="29"/>
+      <c r="O30" s="29"/>
+      <c r="P30" s="29"/>
+      <c r="Q30" s="29"/>
+      <c r="R30" s="29"/>
+      <c r="S30" s="29"/>
+      <c r="T30" s="29"/>
+      <c r="U30" s="30"/>
+      <c r="V30" s="31"/>
+      <c r="W30" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="31" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="A31" s="27">
+        <v>478</v>
+      </c>
+      <c r="B31" s="27" t="s">
+        <v>42</v>
+      </c>
+      <c r="C31" s="32" t="s">
+        <v>48</v>
+      </c>
+      <c r="D31" s="27" t="s">
+        <v>97</v>
+      </c>
+      <c r="E31" s="37" t="s">
+        <v>98</v>
+      </c>
+      <c r="F31" s="28">
         <v>46101</v>
       </c>
-      <c r="G24" s="35" t="s">
-        <v>176</v>
-      </c>
-      <c r="H24" s="35" t="s">
-        <v>179</v>
-      </c>
-      <c r="I24" s="40" t="s">
-        <v>180</v>
-      </c>
-      <c r="J24" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K24" s="36"/>
-      <c r="L24" s="36"/>
-      <c r="M24" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N24" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O24" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P24" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q24" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R24" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S24" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T24" s="36"/>
-      <c r="U24" s="37"/>
-      <c r="V24" s="38"/>
-      <c r="W24" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="25" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A25" s="33">
-        <v>185</v>
-      </c>
-      <c r="B25" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C25" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D25" s="33" t="s">
-        <v>79</v>
-      </c>
-      <c r="E25" s="41" t="s">
-        <v>80</v>
-      </c>
-      <c r="F25" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G25" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="H25" s="35" t="s">
-        <v>182</v>
-      </c>
-      <c r="I25" s="40" t="s">
-        <v>183</v>
-      </c>
-      <c r="J25" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K25" s="36"/>
-      <c r="L25" s="36"/>
-      <c r="M25" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N25" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O25" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P25" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q25" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R25" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S25" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T25" s="36"/>
-      <c r="U25" s="37"/>
-      <c r="V25" s="38"/>
-      <c r="W25" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="26" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A26" s="33">
-        <v>186</v>
-      </c>
-      <c r="B26" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C26" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D26" s="33" t="s">
-        <v>81</v>
-      </c>
-      <c r="E26" s="41" t="s">
-        <v>82</v>
-      </c>
-      <c r="F26" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G26" s="35" t="s">
-        <v>181</v>
-      </c>
-      <c r="H26" s="35" t="s">
-        <v>184</v>
-      </c>
-      <c r="I26" s="40" t="s">
-        <v>185</v>
-      </c>
-      <c r="J26" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K26" s="36"/>
-      <c r="L26" s="36"/>
-      <c r="M26" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N26" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O26" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P26" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q26" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R26" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S26" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T26" s="36"/>
-      <c r="U26" s="37"/>
-      <c r="V26" s="38"/>
-      <c r="W26" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="27" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A27" s="33">
-        <v>187</v>
-      </c>
-      <c r="B27" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C27" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D27" s="33" t="s">
-        <v>83</v>
-      </c>
-      <c r="E27" s="41" t="s">
-        <v>84</v>
-      </c>
-      <c r="F27" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G27" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="H27" s="35" t="s">
-        <v>187</v>
-      </c>
-      <c r="I27" s="40" t="s">
-        <v>188</v>
-      </c>
-      <c r="J27" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K27" s="36"/>
-      <c r="L27" s="36"/>
-      <c r="M27" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N27" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O27" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P27" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q27" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R27" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S27" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T27" s="36"/>
-      <c r="U27" s="37"/>
-      <c r="V27" s="38"/>
-      <c r="W27" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="28" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A28" s="33">
-        <v>188</v>
-      </c>
-      <c r="B28" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C28" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D28" s="33" t="s">
-        <v>85</v>
-      </c>
-      <c r="E28" s="41" t="s">
-        <v>86</v>
-      </c>
-      <c r="F28" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G28" s="35" t="s">
-        <v>186</v>
-      </c>
-      <c r="H28" s="35" t="s">
-        <v>189</v>
-      </c>
-      <c r="I28" s="40" t="s">
-        <v>190</v>
-      </c>
-      <c r="J28" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K28" s="36"/>
-      <c r="L28" s="36"/>
-      <c r="M28" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N28" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O28" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P28" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q28" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R28" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S28" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T28" s="36"/>
-      <c r="U28" s="37"/>
-      <c r="V28" s="38"/>
-      <c r="W28" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="29" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A29" s="33">
-        <v>189</v>
-      </c>
-      <c r="B29" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C29" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D29" s="33" t="s">
-        <v>87</v>
-      </c>
-      <c r="E29" s="41" t="s">
-        <v>88</v>
-      </c>
-      <c r="F29" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G29" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="H29" s="35" t="s">
-        <v>192</v>
-      </c>
-      <c r="I29" s="40" t="s">
-        <v>193</v>
-      </c>
-      <c r="J29" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K29" s="36"/>
-      <c r="L29" s="36"/>
-      <c r="M29" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="N29" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="O29" s="36" t="s">
-        <v>153</v>
-      </c>
-      <c r="P29" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="Q29" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="R29" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="S29" s="36" t="s">
-        <v>163</v>
-      </c>
-      <c r="T29" s="36"/>
-      <c r="U29" s="37"/>
-      <c r="V29" s="38"/>
-      <c r="W29" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="30" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A30" s="33">
-        <v>190</v>
-      </c>
-      <c r="B30" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C30" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D30" s="33" t="s">
-        <v>89</v>
-      </c>
-      <c r="E30" s="41" t="s">
-        <v>90</v>
-      </c>
-      <c r="F30" s="35"/>
-      <c r="G30" s="35"/>
-      <c r="H30" s="35"/>
-      <c r="I30" s="40"/>
-      <c r="J30" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="K30" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="L30" s="36"/>
-      <c r="M30" s="36"/>
-      <c r="N30" s="36"/>
-      <c r="O30" s="36"/>
-      <c r="P30" s="36"/>
-      <c r="Q30" s="36"/>
-      <c r="R30" s="36"/>
-      <c r="S30" s="36"/>
-      <c r="T30" s="36"/>
-      <c r="U30" s="37" t="s">
-        <v>59</v>
-      </c>
-      <c r="V30" s="38"/>
-      <c r="W30" s="36" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="31" spans="1:23" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A31" s="33">
-        <v>469</v>
-      </c>
-      <c r="B31" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C31" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D31" s="33" t="s">
-        <v>92</v>
-      </c>
-      <c r="E31" s="41" t="s">
-        <v>93</v>
-      </c>
-      <c r="F31" s="33"/>
-      <c r="G31" s="33"/>
-      <c r="H31" s="33"/>
-      <c r="I31" s="33"/>
-      <c r="J31" s="36" t="s">
-        <v>148</v>
-      </c>
-      <c r="K31" s="36" t="s">
-        <v>156</v>
-      </c>
-      <c r="L31" s="33"/>
-      <c r="M31" s="36"/>
-      <c r="N31" s="36"/>
-      <c r="O31" s="33"/>
-      <c r="P31" s="36"/>
-      <c r="Q31" s="36"/>
-      <c r="R31" s="36"/>
-      <c r="S31" s="33"/>
-      <c r="T31" s="36"/>
-      <c r="U31" s="33" t="s">
-        <v>59</v>
-      </c>
-      <c r="V31" s="33"/>
-      <c r="W31" s="33" t="s">
-        <v>47</v>
-      </c>
-    </row>
-    <row r="32" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A32" s="33">
-        <v>476</v>
-      </c>
-      <c r="B32" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C32" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D32" s="33" t="s">
-        <v>94</v>
-      </c>
-      <c r="E32" s="41" t="s">
-        <v>95</v>
-      </c>
-      <c r="F32" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G32" s="35" t="s">
-        <v>191</v>
-      </c>
-      <c r="H32" s="35" t="s">
-        <v>194</v>
-      </c>
-      <c r="I32" s="40" t="s">
-        <v>195</v>
-      </c>
-      <c r="J32" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K32" s="36"/>
-      <c r="L32" s="36"/>
-      <c r="M32" s="36"/>
-      <c r="N32" s="36"/>
-      <c r="O32" s="36"/>
-      <c r="P32" s="36"/>
-      <c r="Q32" s="36"/>
-      <c r="R32" s="36"/>
-      <c r="S32" s="36"/>
-      <c r="T32" s="36"/>
-      <c r="U32" s="37"/>
-      <c r="V32" s="38"/>
-      <c r="W32" s="36" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="33" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A33" s="33">
-        <v>477</v>
-      </c>
-      <c r="B33" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C33" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D33" s="33" t="s">
-        <v>96</v>
-      </c>
-      <c r="E33" s="41" t="s">
-        <v>97</v>
-      </c>
-      <c r="F33" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G33" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="H33" s="35" t="s">
-        <v>197</v>
-      </c>
-      <c r="I33" s="40" t="s">
-        <v>198</v>
-      </c>
-      <c r="J33" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K33" s="36"/>
-      <c r="L33" s="36"/>
-      <c r="M33" s="36"/>
-      <c r="N33" s="36"/>
-      <c r="O33" s="36"/>
-      <c r="P33" s="36"/>
-      <c r="Q33" s="36"/>
-      <c r="R33" s="36"/>
-      <c r="S33" s="36"/>
-      <c r="T33" s="36"/>
-      <c r="U33" s="37"/>
-      <c r="V33" s="38"/>
-      <c r="W33" s="36" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="34" spans="1:23" ht="11.1" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A34" s="33">
-        <v>478</v>
-      </c>
-      <c r="B34" s="33" t="s">
-        <v>43</v>
-      </c>
-      <c r="C34" s="39" t="s">
-        <v>49</v>
-      </c>
-      <c r="D34" s="33" t="s">
-        <v>98</v>
-      </c>
-      <c r="E34" s="44" t="s">
-        <v>99</v>
-      </c>
-      <c r="F34" s="35">
-        <v>46101</v>
-      </c>
-      <c r="G34" s="35" t="s">
-        <v>196</v>
-      </c>
-      <c r="H34" s="35" t="s">
+      <c r="G31" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="I34" s="40" t="s">
-        <v>200</v>
-      </c>
-      <c r="J34" s="36" t="s">
-        <v>59</v>
-      </c>
-      <c r="K34" s="36"/>
-      <c r="L34" s="36"/>
-      <c r="M34" s="36"/>
-      <c r="N34" s="36"/>
-      <c r="O34" s="36"/>
-      <c r="P34" s="36"/>
-      <c r="Q34" s="36"/>
-      <c r="R34" s="36"/>
-      <c r="S34" s="36"/>
-      <c r="T34" s="36"/>
-      <c r="U34" s="37"/>
-      <c r="V34" s="38"/>
-      <c r="W34" s="36" t="s">
-        <v>45</v>
-      </c>
-    </row>
-    <row r="35" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="H31" s="28" t="s">
+        <v>202</v>
+      </c>
+      <c r="I31" s="33" t="s">
+        <v>203</v>
+      </c>
+      <c r="J31" s="29" t="s">
+        <v>58</v>
+      </c>
+      <c r="K31" s="29"/>
+      <c r="L31" s="29"/>
+      <c r="M31" s="29"/>
+      <c r="N31" s="29"/>
+      <c r="O31" s="29"/>
+      <c r="P31" s="29"/>
+      <c r="Q31" s="29"/>
+      <c r="R31" s="29"/>
+      <c r="S31" s="29"/>
+      <c r="T31" s="29"/>
+      <c r="U31" s="30"/>
+      <c r="V31" s="31"/>
+      <c r="W31" s="29" t="s">
+        <v>44</v>
+      </c>
+    </row>
+    <row r="32" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F32" s="6"/>
+      <c r="G32" s="6"/>
+      <c r="H32" s="6"/>
+      <c r="I32" s="6"/>
+      <c r="J32" s="7"/>
+      <c r="K32" s="7"/>
+      <c r="L32" s="7"/>
+      <c r="M32" s="7"/>
+      <c r="N32" s="7"/>
+      <c r="O32" s="7"/>
+      <c r="P32" s="7"/>
+      <c r="Q32" s="7"/>
+      <c r="R32" s="7"/>
+      <c r="S32" s="7"/>
+      <c r="T32" s="7"/>
+      <c r="U32" s="8"/>
+      <c r="V32" s="2"/>
+      <c r="W32" s="9"/>
+    </row>
+    <row r="33" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F33" s="6"/>
+      <c r="G33" s="6"/>
+      <c r="H33" s="6"/>
+      <c r="I33" s="6"/>
+      <c r="J33" s="7"/>
+      <c r="K33" s="7"/>
+      <c r="L33" s="7"/>
+      <c r="M33" s="7"/>
+      <c r="N33" s="7"/>
+      <c r="O33" s="7"/>
+      <c r="P33" s="7"/>
+      <c r="Q33" s="7"/>
+      <c r="R33" s="7"/>
+      <c r="S33" s="7"/>
+      <c r="T33" s="7"/>
+      <c r="U33" s="8"/>
+      <c r="V33" s="2"/>
+      <c r="W33" s="9"/>
+    </row>
+    <row r="34" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="F34" s="6"/>
+      <c r="G34" s="6"/>
+      <c r="H34" s="6"/>
+      <c r="I34" s="6"/>
+      <c r="J34" s="7"/>
+      <c r="K34" s="7"/>
+      <c r="L34" s="7"/>
+      <c r="M34" s="7"/>
+      <c r="N34" s="7"/>
+      <c r="O34" s="7"/>
+      <c r="P34" s="7"/>
+      <c r="Q34" s="7"/>
+      <c r="R34" s="7"/>
+      <c r="S34" s="7"/>
+      <c r="T34" s="7"/>
+      <c r="U34" s="8"/>
+      <c r="V34" s="2"/>
+      <c r="W34" s="9"/>
+    </row>
+    <row r="35" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F35" s="6"/>
       <c r="G35" s="6"/>
       <c r="H35" s="6"/>
@@ -4505,7 +4572,7 @@
       <c r="V35" s="2"/>
       <c r="W35" s="9"/>
     </row>
-    <row r="36" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="36" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F36" s="6"/>
       <c r="G36" s="6"/>
       <c r="H36" s="6"/>
@@ -4525,7 +4592,7 @@
       <c r="V36" s="2"/>
       <c r="W36" s="9"/>
     </row>
-    <row r="37" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="37" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F37" s="6"/>
       <c r="G37" s="6"/>
       <c r="H37" s="6"/>
@@ -4545,7 +4612,7 @@
       <c r="V37" s="2"/>
       <c r="W37" s="9"/>
     </row>
-    <row r="38" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="38" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F38" s="6"/>
       <c r="G38" s="6"/>
       <c r="H38" s="6"/>
@@ -4565,7 +4632,7 @@
       <c r="V38" s="2"/>
       <c r="W38" s="9"/>
     </row>
-    <row r="39" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="39" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F39" s="6"/>
       <c r="G39" s="6"/>
       <c r="H39" s="6"/>
@@ -4585,7 +4652,7 @@
       <c r="V39" s="2"/>
       <c r="W39" s="9"/>
     </row>
-    <row r="40" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="40" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F40" s="6"/>
       <c r="G40" s="6"/>
       <c r="H40" s="6"/>
@@ -4605,7 +4672,7 @@
       <c r="V40" s="2"/>
       <c r="W40" s="9"/>
     </row>
-    <row r="41" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="41" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F41" s="6"/>
       <c r="G41" s="6"/>
       <c r="H41" s="6"/>
@@ -4625,7 +4692,7 @@
       <c r="V41" s="2"/>
       <c r="W41" s="9"/>
     </row>
-    <row r="42" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="42" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F42" s="6"/>
       <c r="G42" s="6"/>
       <c r="H42" s="6"/>
@@ -4645,7 +4712,7 @@
       <c r="V42" s="2"/>
       <c r="W42" s="9"/>
     </row>
-    <row r="43" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="43" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F43" s="6"/>
       <c r="G43" s="6"/>
       <c r="H43" s="6"/>
@@ -4665,7 +4732,7 @@
       <c r="V43" s="2"/>
       <c r="W43" s="9"/>
     </row>
-    <row r="44" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="44" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F44" s="6"/>
       <c r="G44" s="6"/>
       <c r="H44" s="6"/>
@@ -4685,7 +4752,7 @@
       <c r="V44" s="2"/>
       <c r="W44" s="9"/>
     </row>
-    <row r="45" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="45" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F45" s="6"/>
       <c r="G45" s="6"/>
       <c r="H45" s="6"/>
@@ -4705,7 +4772,7 @@
       <c r="V45" s="2"/>
       <c r="W45" s="9"/>
     </row>
-    <row r="46" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="46" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F46" s="6"/>
       <c r="G46" s="6"/>
       <c r="H46" s="6"/>
@@ -4725,7 +4792,7 @@
       <c r="V46" s="2"/>
       <c r="W46" s="9"/>
     </row>
-    <row r="47" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="47" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F47" s="6"/>
       <c r="G47" s="6"/>
       <c r="H47" s="6"/>
@@ -4745,7 +4812,7 @@
       <c r="V47" s="2"/>
       <c r="W47" s="9"/>
     </row>
-    <row r="48" spans="1:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="48" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="F48" s="6"/>
       <c r="G48" s="6"/>
       <c r="H48" s="6"/>
@@ -5346,887 +5413,156 @@
       <c r="W77" s="9"/>
     </row>
     <row r="78" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F78" s="6"/>
-      <c r="G78" s="6"/>
-      <c r="H78" s="6"/>
-      <c r="I78" s="6"/>
-      <c r="J78" s="7"/>
-      <c r="K78" s="7"/>
-      <c r="L78" s="7"/>
-      <c r="M78" s="7"/>
-      <c r="N78" s="7"/>
-      <c r="O78" s="7"/>
-      <c r="P78" s="7"/>
-      <c r="Q78" s="7"/>
-      <c r="R78" s="7"/>
-      <c r="S78" s="7"/>
-      <c r="T78" s="7"/>
-      <c r="U78" s="8"/>
-      <c r="V78" s="2"/>
-      <c r="W78" s="9"/>
+      <c r="W78" s="7"/>
     </row>
     <row r="79" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F79" s="6"/>
-      <c r="G79" s="6"/>
-      <c r="H79" s="6"/>
-      <c r="I79" s="6"/>
-      <c r="J79" s="7"/>
-      <c r="K79" s="7"/>
-      <c r="L79" s="7"/>
-      <c r="M79" s="7"/>
-      <c r="N79" s="7"/>
-      <c r="O79" s="7"/>
-      <c r="P79" s="7"/>
-      <c r="Q79" s="7"/>
-      <c r="R79" s="7"/>
-      <c r="S79" s="7"/>
-      <c r="T79" s="7"/>
-      <c r="U79" s="8"/>
-      <c r="V79" s="2"/>
-      <c r="W79" s="9"/>
+      <c r="W79" s="7"/>
     </row>
     <row r="80" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F80" s="6"/>
-      <c r="G80" s="6"/>
-      <c r="H80" s="6"/>
-      <c r="I80" s="6"/>
-      <c r="J80" s="7"/>
-      <c r="K80" s="7"/>
-      <c r="L80" s="7"/>
-      <c r="M80" s="7"/>
-      <c r="N80" s="7"/>
-      <c r="O80" s="7"/>
-      <c r="P80" s="7"/>
-      <c r="Q80" s="7"/>
-      <c r="R80" s="7"/>
-      <c r="S80" s="7"/>
-      <c r="T80" s="7"/>
-      <c r="U80" s="8"/>
-      <c r="V80" s="2"/>
-      <c r="W80" s="9"/>
-    </row>
-    <row r="81" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F81" s="6"/>
-      <c r="G81" s="6"/>
-      <c r="H81" s="6"/>
-      <c r="I81" s="6"/>
-      <c r="J81" s="7"/>
-      <c r="K81" s="7"/>
-      <c r="L81" s="7"/>
-      <c r="M81" s="7"/>
-      <c r="N81" s="7"/>
-      <c r="O81" s="7"/>
-      <c r="P81" s="7"/>
-      <c r="Q81" s="7"/>
-      <c r="R81" s="7"/>
-      <c r="S81" s="7"/>
-      <c r="T81" s="7"/>
-      <c r="U81" s="8"/>
-      <c r="V81" s="2"/>
-      <c r="W81" s="9"/>
-    </row>
-    <row r="82" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F82" s="6"/>
-      <c r="G82" s="6"/>
-      <c r="H82" s="6"/>
-      <c r="I82" s="6"/>
-      <c r="J82" s="7"/>
-      <c r="K82" s="7"/>
-      <c r="L82" s="7"/>
-      <c r="M82" s="7"/>
-      <c r="N82" s="7"/>
-      <c r="O82" s="7"/>
-      <c r="P82" s="7"/>
-      <c r="Q82" s="7"/>
-      <c r="R82" s="7"/>
-      <c r="S82" s="7"/>
-      <c r="T82" s="7"/>
-      <c r="U82" s="8"/>
-      <c r="V82" s="2"/>
-      <c r="W82" s="9"/>
-    </row>
-    <row r="83" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F83" s="6"/>
-      <c r="G83" s="6"/>
-      <c r="H83" s="6"/>
-      <c r="I83" s="6"/>
-      <c r="J83" s="7"/>
-      <c r="K83" s="7"/>
-      <c r="L83" s="7"/>
-      <c r="M83" s="7"/>
-      <c r="N83" s="7"/>
-      <c r="O83" s="7"/>
-      <c r="P83" s="7"/>
-      <c r="Q83" s="7"/>
-      <c r="R83" s="7"/>
-      <c r="S83" s="7"/>
-      <c r="T83" s="7"/>
-      <c r="U83" s="8"/>
-      <c r="V83" s="2"/>
-      <c r="W83" s="9"/>
-    </row>
-    <row r="84" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F84" s="6"/>
-      <c r="G84" s="6"/>
-      <c r="H84" s="6"/>
-      <c r="I84" s="6"/>
-      <c r="J84" s="7"/>
-      <c r="K84" s="7"/>
-      <c r="L84" s="7"/>
-      <c r="M84" s="7"/>
-      <c r="N84" s="7"/>
-      <c r="O84" s="7"/>
-      <c r="P84" s="7"/>
-      <c r="Q84" s="7"/>
-      <c r="R84" s="7"/>
-      <c r="S84" s="7"/>
-      <c r="T84" s="7"/>
-      <c r="U84" s="8"/>
-      <c r="V84" s="2"/>
-      <c r="W84" s="9"/>
-    </row>
-    <row r="85" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F85" s="6"/>
-      <c r="G85" s="6"/>
-      <c r="H85" s="6"/>
-      <c r="I85" s="6"/>
-      <c r="J85" s="7"/>
-      <c r="K85" s="7"/>
-      <c r="L85" s="7"/>
-      <c r="M85" s="7"/>
-      <c r="N85" s="7"/>
-      <c r="O85" s="7"/>
-      <c r="P85" s="7"/>
-      <c r="Q85" s="7"/>
-      <c r="R85" s="7"/>
-      <c r="S85" s="7"/>
-      <c r="T85" s="7"/>
-      <c r="U85" s="8"/>
-      <c r="V85" s="2"/>
-      <c r="W85" s="9"/>
-    </row>
-    <row r="86" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F86" s="6"/>
-      <c r="G86" s="6"/>
-      <c r="H86" s="6"/>
-      <c r="I86" s="6"/>
-      <c r="J86" s="7"/>
-      <c r="K86" s="7"/>
-      <c r="L86" s="7"/>
-      <c r="M86" s="7"/>
-      <c r="N86" s="7"/>
-      <c r="O86" s="7"/>
-      <c r="P86" s="7"/>
-      <c r="Q86" s="7"/>
-      <c r="R86" s="7"/>
-      <c r="S86" s="7"/>
-      <c r="T86" s="7"/>
-      <c r="U86" s="8"/>
-      <c r="V86" s="2"/>
-      <c r="W86" s="9"/>
-    </row>
-    <row r="87" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F87" s="6"/>
-      <c r="G87" s="6"/>
-      <c r="H87" s="6"/>
-      <c r="I87" s="6"/>
-      <c r="J87" s="7"/>
-      <c r="K87" s="7"/>
-      <c r="L87" s="7"/>
-      <c r="M87" s="7"/>
-      <c r="N87" s="7"/>
-      <c r="O87" s="7"/>
-      <c r="P87" s="7"/>
-      <c r="Q87" s="7"/>
-      <c r="R87" s="7"/>
-      <c r="S87" s="7"/>
-      <c r="T87" s="7"/>
-      <c r="U87" s="8"/>
-      <c r="V87" s="2"/>
-      <c r="W87" s="9"/>
-    </row>
-    <row r="88" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F88" s="6"/>
-      <c r="G88" s="6"/>
-      <c r="H88" s="6"/>
-      <c r="I88" s="6"/>
-      <c r="J88" s="7"/>
-      <c r="K88" s="7"/>
-      <c r="L88" s="7"/>
-      <c r="M88" s="7"/>
-      <c r="N88" s="7"/>
-      <c r="O88" s="7"/>
-      <c r="P88" s="7"/>
-      <c r="Q88" s="7"/>
-      <c r="R88" s="7"/>
-      <c r="S88" s="7"/>
-      <c r="T88" s="7"/>
-      <c r="U88" s="8"/>
-      <c r="V88" s="2"/>
-      <c r="W88" s="9"/>
-    </row>
-    <row r="89" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F89" s="6"/>
-      <c r="G89" s="6"/>
-      <c r="H89" s="6"/>
-      <c r="I89" s="6"/>
-      <c r="J89" s="7"/>
-      <c r="K89" s="7"/>
-      <c r="L89" s="7"/>
-      <c r="M89" s="7"/>
-      <c r="N89" s="7"/>
-      <c r="O89" s="7"/>
-      <c r="P89" s="7"/>
-      <c r="Q89" s="7"/>
-      <c r="R89" s="7"/>
-      <c r="S89" s="7"/>
-      <c r="T89" s="7"/>
-      <c r="U89" s="8"/>
-      <c r="V89" s="2"/>
-      <c r="W89" s="9"/>
-    </row>
-    <row r="90" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F90" s="6"/>
-      <c r="G90" s="6"/>
-      <c r="H90" s="6"/>
-      <c r="I90" s="6"/>
-      <c r="J90" s="7"/>
-      <c r="K90" s="7"/>
-      <c r="L90" s="7"/>
-      <c r="M90" s="7"/>
-      <c r="N90" s="7"/>
-      <c r="O90" s="7"/>
-      <c r="P90" s="7"/>
-      <c r="Q90" s="7"/>
-      <c r="R90" s="7"/>
-      <c r="S90" s="7"/>
-      <c r="T90" s="7"/>
-      <c r="U90" s="8"/>
-      <c r="V90" s="2"/>
-      <c r="W90" s="9"/>
-    </row>
-    <row r="91" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F91" s="6"/>
-      <c r="G91" s="6"/>
-      <c r="H91" s="6"/>
-      <c r="I91" s="6"/>
-      <c r="J91" s="7"/>
-      <c r="K91" s="7"/>
-      <c r="L91" s="7"/>
-      <c r="M91" s="7"/>
-      <c r="N91" s="7"/>
-      <c r="O91" s="7"/>
-      <c r="P91" s="7"/>
-      <c r="Q91" s="7"/>
-      <c r="R91" s="7"/>
-      <c r="S91" s="7"/>
-      <c r="T91" s="7"/>
-      <c r="U91" s="8"/>
-      <c r="V91" s="2"/>
-      <c r="W91" s="9"/>
-    </row>
-    <row r="92" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F92" s="6"/>
-      <c r="G92" s="6"/>
-      <c r="H92" s="6"/>
-      <c r="I92" s="6"/>
-      <c r="J92" s="7"/>
-      <c r="K92" s="7"/>
-      <c r="L92" s="7"/>
-      <c r="M92" s="7"/>
-      <c r="N92" s="7"/>
-      <c r="O92" s="7"/>
-      <c r="P92" s="7"/>
-      <c r="Q92" s="7"/>
-      <c r="R92" s="7"/>
-      <c r="S92" s="7"/>
-      <c r="T92" s="7"/>
-      <c r="U92" s="8"/>
-      <c r="V92" s="2"/>
-      <c r="W92" s="9"/>
-    </row>
-    <row r="93" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F93" s="6"/>
-      <c r="G93" s="6"/>
-      <c r="H93" s="6"/>
-      <c r="I93" s="6"/>
-      <c r="J93" s="7"/>
-      <c r="K93" s="7"/>
-      <c r="L93" s="7"/>
-      <c r="M93" s="7"/>
-      <c r="N93" s="7"/>
-      <c r="O93" s="7"/>
-      <c r="P93" s="7"/>
-      <c r="Q93" s="7"/>
-      <c r="R93" s="7"/>
-      <c r="S93" s="7"/>
-      <c r="T93" s="7"/>
-      <c r="U93" s="8"/>
-      <c r="V93" s="2"/>
-      <c r="W93" s="9"/>
-    </row>
-    <row r="94" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F94" s="6"/>
-      <c r="G94" s="6"/>
-      <c r="H94" s="6"/>
-      <c r="I94" s="6"/>
-      <c r="J94" s="7"/>
-      <c r="K94" s="7"/>
-      <c r="L94" s="7"/>
-      <c r="M94" s="7"/>
-      <c r="N94" s="7"/>
-      <c r="O94" s="7"/>
-      <c r="P94" s="7"/>
-      <c r="Q94" s="7"/>
-      <c r="R94" s="7"/>
-      <c r="S94" s="7"/>
-      <c r="T94" s="7"/>
-      <c r="U94" s="8"/>
-      <c r="V94" s="2"/>
-      <c r="W94" s="9"/>
-    </row>
-    <row r="95" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F95" s="6"/>
-      <c r="G95" s="6"/>
-      <c r="H95" s="6"/>
-      <c r="I95" s="6"/>
-      <c r="J95" s="7"/>
-      <c r="K95" s="7"/>
-      <c r="L95" s="7"/>
-      <c r="M95" s="7"/>
-      <c r="N95" s="7"/>
-      <c r="O95" s="7"/>
-      <c r="P95" s="7"/>
-      <c r="Q95" s="7"/>
-      <c r="R95" s="7"/>
-      <c r="S95" s="7"/>
-      <c r="T95" s="7"/>
-      <c r="U95" s="8"/>
-      <c r="V95" s="2"/>
-      <c r="W95" s="9"/>
-    </row>
-    <row r="96" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F96" s="6"/>
-      <c r="G96" s="6"/>
-      <c r="H96" s="6"/>
-      <c r="I96" s="6"/>
-      <c r="J96" s="7"/>
-      <c r="K96" s="7"/>
-      <c r="L96" s="7"/>
-      <c r="M96" s="7"/>
-      <c r="N96" s="7"/>
-      <c r="O96" s="7"/>
-      <c r="P96" s="7"/>
-      <c r="Q96" s="7"/>
-      <c r="R96" s="7"/>
-      <c r="S96" s="7"/>
-      <c r="T96" s="7"/>
-      <c r="U96" s="8"/>
-      <c r="V96" s="2"/>
-      <c r="W96" s="9"/>
-    </row>
-    <row r="97" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F97" s="6"/>
-      <c r="G97" s="6"/>
-      <c r="H97" s="6"/>
-      <c r="I97" s="6"/>
-      <c r="J97" s="7"/>
-      <c r="K97" s="7"/>
-      <c r="L97" s="7"/>
-      <c r="M97" s="7"/>
-      <c r="N97" s="7"/>
-      <c r="O97" s="7"/>
-      <c r="P97" s="7"/>
-      <c r="Q97" s="7"/>
-      <c r="R97" s="7"/>
-      <c r="S97" s="7"/>
-      <c r="T97" s="7"/>
-      <c r="U97" s="8"/>
-      <c r="V97" s="2"/>
-      <c r="W97" s="9"/>
-    </row>
-    <row r="98" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F98" s="6"/>
-      <c r="G98" s="6"/>
-      <c r="H98" s="6"/>
-      <c r="I98" s="6"/>
-      <c r="J98" s="7"/>
-      <c r="K98" s="7"/>
-      <c r="L98" s="7"/>
-      <c r="M98" s="7"/>
-      <c r="N98" s="7"/>
-      <c r="O98" s="7"/>
-      <c r="P98" s="7"/>
-      <c r="Q98" s="7"/>
-      <c r="R98" s="7"/>
-      <c r="S98" s="7"/>
-      <c r="T98" s="7"/>
-      <c r="U98" s="8"/>
-      <c r="V98" s="2"/>
-      <c r="W98" s="9"/>
-    </row>
-    <row r="99" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F99" s="6"/>
-      <c r="G99" s="6"/>
-      <c r="H99" s="6"/>
-      <c r="I99" s="6"/>
-      <c r="J99" s="7"/>
-      <c r="K99" s="7"/>
-      <c r="L99" s="7"/>
-      <c r="M99" s="7"/>
-      <c r="N99" s="7"/>
-      <c r="O99" s="7"/>
-      <c r="P99" s="7"/>
-      <c r="Q99" s="7"/>
-      <c r="R99" s="7"/>
-      <c r="S99" s="7"/>
-      <c r="T99" s="7"/>
-      <c r="U99" s="8"/>
-      <c r="V99" s="2"/>
-      <c r="W99" s="9"/>
-    </row>
-    <row r="100" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F100" s="6"/>
-      <c r="G100" s="6"/>
-      <c r="H100" s="6"/>
-      <c r="I100" s="6"/>
-      <c r="J100" s="7"/>
-      <c r="K100" s="7"/>
-      <c r="L100" s="7"/>
-      <c r="M100" s="7"/>
-      <c r="N100" s="7"/>
-      <c r="O100" s="7"/>
-      <c r="P100" s="7"/>
-      <c r="Q100" s="7"/>
-      <c r="R100" s="7"/>
-      <c r="S100" s="7"/>
-      <c r="T100" s="7"/>
-      <c r="U100" s="8"/>
-      <c r="V100" s="2"/>
-      <c r="W100" s="9"/>
-    </row>
-    <row r="101" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F101" s="6"/>
-      <c r="G101" s="6"/>
-      <c r="H101" s="6"/>
-      <c r="I101" s="6"/>
-      <c r="J101" s="7"/>
-      <c r="K101" s="7"/>
-      <c r="L101" s="7"/>
-      <c r="M101" s="7"/>
-      <c r="N101" s="7"/>
-      <c r="O101" s="7"/>
-      <c r="P101" s="7"/>
-      <c r="Q101" s="7"/>
-      <c r="R101" s="7"/>
-      <c r="S101" s="7"/>
-      <c r="T101" s="7"/>
-      <c r="U101" s="8"/>
-      <c r="V101" s="2"/>
-      <c r="W101" s="9"/>
-    </row>
-    <row r="102" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F102" s="6"/>
-      <c r="G102" s="6"/>
-      <c r="H102" s="6"/>
-      <c r="I102" s="6"/>
-      <c r="J102" s="7"/>
-      <c r="K102" s="7"/>
-      <c r="L102" s="7"/>
-      <c r="M102" s="7"/>
-      <c r="N102" s="7"/>
-      <c r="O102" s="7"/>
-      <c r="P102" s="7"/>
-      <c r="Q102" s="7"/>
-      <c r="R102" s="7"/>
-      <c r="S102" s="7"/>
-      <c r="T102" s="7"/>
-      <c r="U102" s="8"/>
-      <c r="V102" s="2"/>
-      <c r="W102" s="9"/>
-    </row>
-    <row r="103" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F103" s="6"/>
-      <c r="G103" s="6"/>
-      <c r="H103" s="6"/>
-      <c r="I103" s="6"/>
-      <c r="J103" s="7"/>
-      <c r="K103" s="7"/>
-      <c r="L103" s="7"/>
-      <c r="M103" s="7"/>
-      <c r="N103" s="7"/>
-      <c r="O103" s="7"/>
-      <c r="P103" s="7"/>
-      <c r="Q103" s="7"/>
-      <c r="R103" s="7"/>
-      <c r="S103" s="7"/>
-      <c r="T103" s="7"/>
-      <c r="U103" s="8"/>
-      <c r="V103" s="2"/>
-      <c r="W103" s="9"/>
-    </row>
-    <row r="104" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F104" s="6"/>
-      <c r="G104" s="6"/>
-      <c r="H104" s="6"/>
-      <c r="I104" s="6"/>
-      <c r="J104" s="7"/>
-      <c r="K104" s="7"/>
-      <c r="L104" s="7"/>
-      <c r="M104" s="7"/>
-      <c r="N104" s="7"/>
-      <c r="O104" s="7"/>
-      <c r="P104" s="7"/>
-      <c r="Q104" s="7"/>
-      <c r="R104" s="7"/>
-      <c r="S104" s="7"/>
-      <c r="T104" s="7"/>
-      <c r="U104" s="8"/>
-      <c r="V104" s="2"/>
-      <c r="W104" s="9"/>
-    </row>
-    <row r="105" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F105" s="6"/>
-      <c r="G105" s="6"/>
-      <c r="H105" s="6"/>
-      <c r="I105" s="6"/>
-      <c r="J105" s="7"/>
-      <c r="K105" s="7"/>
-      <c r="L105" s="7"/>
-      <c r="M105" s="7"/>
-      <c r="N105" s="7"/>
-      <c r="O105" s="7"/>
-      <c r="P105" s="7"/>
-      <c r="Q105" s="7"/>
-      <c r="R105" s="7"/>
-      <c r="S105" s="7"/>
-      <c r="T105" s="7"/>
-      <c r="U105" s="8"/>
-      <c r="V105" s="2"/>
-      <c r="W105" s="9"/>
-    </row>
-    <row r="106" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F106" s="6"/>
-      <c r="G106" s="6"/>
-      <c r="H106" s="6"/>
-      <c r="I106" s="6"/>
-      <c r="J106" s="7"/>
-      <c r="K106" s="7"/>
-      <c r="L106" s="7"/>
-      <c r="M106" s="7"/>
-      <c r="N106" s="7"/>
-      <c r="O106" s="7"/>
-      <c r="P106" s="7"/>
-      <c r="Q106" s="7"/>
-      <c r="R106" s="7"/>
-      <c r="S106" s="7"/>
-      <c r="T106" s="7"/>
-      <c r="U106" s="8"/>
-      <c r="V106" s="2"/>
-      <c r="W106" s="9"/>
-    </row>
-    <row r="107" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F107" s="6"/>
-      <c r="G107" s="6"/>
-      <c r="H107" s="6"/>
-      <c r="I107" s="6"/>
-      <c r="J107" s="7"/>
-      <c r="K107" s="7"/>
-      <c r="L107" s="7"/>
-      <c r="M107" s="7"/>
-      <c r="N107" s="7"/>
-      <c r="O107" s="7"/>
-      <c r="P107" s="7"/>
-      <c r="Q107" s="7"/>
-      <c r="R107" s="7"/>
-      <c r="S107" s="7"/>
-      <c r="T107" s="7"/>
-      <c r="U107" s="8"/>
-      <c r="V107" s="2"/>
-      <c r="W107" s="9"/>
-    </row>
-    <row r="108" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F108" s="6"/>
-      <c r="G108" s="6"/>
-      <c r="H108" s="6"/>
-      <c r="I108" s="6"/>
-      <c r="J108" s="7"/>
-      <c r="K108" s="7"/>
-      <c r="L108" s="7"/>
-      <c r="M108" s="7"/>
-      <c r="N108" s="7"/>
-      <c r="O108" s="7"/>
-      <c r="P108" s="7"/>
-      <c r="Q108" s="7"/>
-      <c r="R108" s="7"/>
-      <c r="S108" s="7"/>
-      <c r="T108" s="7"/>
-      <c r="U108" s="8"/>
-      <c r="V108" s="2"/>
-      <c r="W108" s="9"/>
-    </row>
-    <row r="109" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F109" s="6"/>
-      <c r="G109" s="6"/>
-      <c r="H109" s="6"/>
-      <c r="I109" s="6"/>
-      <c r="J109" s="7"/>
-      <c r="K109" s="7"/>
-      <c r="L109" s="7"/>
-      <c r="M109" s="7"/>
-      <c r="N109" s="7"/>
-      <c r="O109" s="7"/>
-      <c r="P109" s="7"/>
-      <c r="Q109" s="7"/>
-      <c r="R109" s="7"/>
-      <c r="S109" s="7"/>
-      <c r="T109" s="7"/>
-      <c r="U109" s="8"/>
-      <c r="V109" s="2"/>
-      <c r="W109" s="9"/>
-    </row>
-    <row r="110" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F110" s="6"/>
-      <c r="G110" s="6"/>
-      <c r="H110" s="6"/>
-      <c r="I110" s="6"/>
-      <c r="J110" s="7"/>
-      <c r="K110" s="7"/>
-      <c r="L110" s="7"/>
-      <c r="M110" s="7"/>
-      <c r="N110" s="7"/>
-      <c r="O110" s="7"/>
-      <c r="P110" s="7"/>
-      <c r="Q110" s="7"/>
-      <c r="R110" s="7"/>
-      <c r="S110" s="7"/>
-      <c r="T110" s="7"/>
-      <c r="U110" s="8"/>
-      <c r="V110" s="2"/>
-      <c r="W110" s="9"/>
-    </row>
-    <row r="111" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F111" s="6"/>
-      <c r="G111" s="6"/>
-      <c r="H111" s="6"/>
-      <c r="I111" s="6"/>
-      <c r="J111" s="7"/>
-      <c r="K111" s="7"/>
-      <c r="L111" s="7"/>
-      <c r="M111" s="7"/>
-      <c r="N111" s="7"/>
-      <c r="O111" s="7"/>
-      <c r="P111" s="7"/>
-      <c r="Q111" s="7"/>
-      <c r="R111" s="7"/>
-      <c r="S111" s="7"/>
-      <c r="T111" s="7"/>
-      <c r="U111" s="8"/>
-      <c r="V111" s="2"/>
-      <c r="W111" s="9"/>
-    </row>
-    <row r="112" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F112" s="6"/>
-      <c r="G112" s="6"/>
-      <c r="H112" s="6"/>
-      <c r="I112" s="6"/>
-      <c r="J112" s="7"/>
-      <c r="K112" s="7"/>
-      <c r="L112" s="7"/>
-      <c r="M112" s="7"/>
-      <c r="N112" s="7"/>
-      <c r="O112" s="7"/>
-      <c r="P112" s="7"/>
-      <c r="Q112" s="7"/>
-      <c r="R112" s="7"/>
-      <c r="S112" s="7"/>
-      <c r="T112" s="7"/>
-      <c r="U112" s="8"/>
-      <c r="V112" s="2"/>
-      <c r="W112" s="9"/>
-    </row>
-    <row r="113" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F113" s="6"/>
-      <c r="G113" s="6"/>
-      <c r="H113" s="6"/>
-      <c r="I113" s="6"/>
-      <c r="J113" s="7"/>
-      <c r="K113" s="7"/>
-      <c r="L113" s="7"/>
-      <c r="M113" s="7"/>
-      <c r="N113" s="7"/>
-      <c r="O113" s="7"/>
-      <c r="P113" s="7"/>
-      <c r="Q113" s="7"/>
-      <c r="R113" s="7"/>
-      <c r="S113" s="7"/>
-      <c r="T113" s="7"/>
-      <c r="U113" s="8"/>
-      <c r="V113" s="2"/>
-      <c r="W113" s="9"/>
-    </row>
-    <row r="114" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F114" s="6"/>
-      <c r="G114" s="6"/>
-      <c r="H114" s="6"/>
-      <c r="I114" s="6"/>
-      <c r="J114" s="7"/>
-      <c r="K114" s="7"/>
-      <c r="L114" s="7"/>
-      <c r="M114" s="7"/>
-      <c r="N114" s="7"/>
-      <c r="O114" s="7"/>
-      <c r="P114" s="7"/>
-      <c r="Q114" s="7"/>
-      <c r="R114" s="7"/>
-      <c r="S114" s="7"/>
-      <c r="T114" s="7"/>
-      <c r="U114" s="8"/>
-      <c r="V114" s="2"/>
-      <c r="W114" s="9"/>
-    </row>
-    <row r="115" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F115" s="6"/>
-      <c r="G115" s="6"/>
-      <c r="H115" s="6"/>
-      <c r="I115" s="6"/>
-      <c r="J115" s="7"/>
-      <c r="K115" s="7"/>
-      <c r="L115" s="7"/>
-      <c r="M115" s="7"/>
-      <c r="N115" s="7"/>
-      <c r="O115" s="7"/>
-      <c r="P115" s="7"/>
-      <c r="Q115" s="7"/>
-      <c r="R115" s="7"/>
-      <c r="S115" s="7"/>
-      <c r="T115" s="7"/>
-      <c r="U115" s="8"/>
-      <c r="V115" s="2"/>
-      <c r="W115" s="9"/>
-    </row>
-    <row r="116" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F116" s="6"/>
-      <c r="G116" s="6"/>
-      <c r="H116" s="6"/>
-      <c r="I116" s="6"/>
-      <c r="J116" s="7"/>
-      <c r="K116" s="7"/>
-      <c r="L116" s="7"/>
-      <c r="M116" s="7"/>
-      <c r="N116" s="7"/>
-      <c r="O116" s="7"/>
-      <c r="P116" s="7"/>
-      <c r="Q116" s="7"/>
-      <c r="R116" s="7"/>
-      <c r="S116" s="7"/>
-      <c r="T116" s="7"/>
-      <c r="U116" s="8"/>
-      <c r="V116" s="2"/>
-      <c r="W116" s="9"/>
-    </row>
-    <row r="117" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F117" s="6"/>
-      <c r="G117" s="6"/>
-      <c r="H117" s="6"/>
-      <c r="I117" s="6"/>
-      <c r="J117" s="7"/>
-      <c r="K117" s="7"/>
-      <c r="L117" s="7"/>
-      <c r="M117" s="7"/>
-      <c r="N117" s="7"/>
-      <c r="O117" s="7"/>
-      <c r="P117" s="7"/>
-      <c r="Q117" s="7"/>
-      <c r="R117" s="7"/>
-      <c r="S117" s="7"/>
-      <c r="T117" s="7"/>
-      <c r="U117" s="8"/>
-      <c r="V117" s="2"/>
-      <c r="W117" s="9"/>
-    </row>
-    <row r="118" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F118" s="6"/>
-      <c r="G118" s="6"/>
-      <c r="H118" s="6"/>
-      <c r="I118" s="6"/>
-      <c r="J118" s="7"/>
-      <c r="K118" s="7"/>
-      <c r="L118" s="7"/>
-      <c r="M118" s="7"/>
-      <c r="N118" s="7"/>
-      <c r="O118" s="7"/>
-      <c r="P118" s="7"/>
-      <c r="Q118" s="7"/>
-      <c r="R118" s="7"/>
-      <c r="S118" s="7"/>
-      <c r="T118" s="7"/>
-      <c r="U118" s="8"/>
-      <c r="V118" s="2"/>
-      <c r="W118" s="9"/>
-    </row>
-    <row r="119" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F119" s="6"/>
-      <c r="G119" s="6"/>
-      <c r="H119" s="6"/>
-      <c r="I119" s="6"/>
-      <c r="J119" s="7"/>
-      <c r="K119" s="7"/>
-      <c r="L119" s="7"/>
-      <c r="M119" s="7"/>
-      <c r="N119" s="7"/>
-      <c r="O119" s="7"/>
-      <c r="P119" s="7"/>
-      <c r="Q119" s="7"/>
-      <c r="R119" s="7"/>
-      <c r="S119" s="7"/>
-      <c r="T119" s="7"/>
-      <c r="U119" s="8"/>
-      <c r="V119" s="2"/>
-      <c r="W119" s="9"/>
-    </row>
-    <row r="120" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="F120" s="6"/>
-      <c r="G120" s="6"/>
-      <c r="H120" s="6"/>
-      <c r="I120" s="6"/>
-      <c r="J120" s="7"/>
-      <c r="K120" s="7"/>
-      <c r="L120" s="7"/>
-      <c r="M120" s="7"/>
-      <c r="N120" s="7"/>
-      <c r="O120" s="7"/>
-      <c r="P120" s="7"/>
-      <c r="Q120" s="7"/>
-      <c r="R120" s="7"/>
-      <c r="S120" s="7"/>
-      <c r="T120" s="7"/>
-      <c r="U120" s="8"/>
-      <c r="V120" s="2"/>
-      <c r="W120" s="9"/>
-    </row>
-    <row r="121" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W80" s="7"/>
+    </row>
+    <row r="81" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W81" s="7"/>
+    </row>
+    <row r="82" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W82" s="7"/>
+    </row>
+    <row r="83" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W83" s="7"/>
+    </row>
+    <row r="84" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W84" s="7"/>
+    </row>
+    <row r="85" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W85" s="7"/>
+    </row>
+    <row r="86" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W86" s="7"/>
+    </row>
+    <row r="87" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W87" s="7"/>
+    </row>
+    <row r="88" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W88" s="7"/>
+    </row>
+    <row r="89" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W89" s="7"/>
+    </row>
+    <row r="90" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W90" s="7"/>
+    </row>
+    <row r="91" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W91" s="7"/>
+    </row>
+    <row r="92" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W92" s="7"/>
+    </row>
+    <row r="93" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W93" s="7"/>
+    </row>
+    <row r="94" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W94" s="7"/>
+    </row>
+    <row r="95" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W95" s="7"/>
+    </row>
+    <row r="96" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W96" s="7"/>
+    </row>
+    <row r="97" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W97" s="7"/>
+    </row>
+    <row r="98" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W98" s="7"/>
+    </row>
+    <row r="99" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W99" s="7"/>
+    </row>
+    <row r="100" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W100" s="7"/>
+    </row>
+    <row r="101" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W101" s="7"/>
+    </row>
+    <row r="102" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W102" s="7"/>
+    </row>
+    <row r="103" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W103" s="7"/>
+    </row>
+    <row r="104" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W104" s="7"/>
+    </row>
+    <row r="105" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W105" s="7"/>
+    </row>
+    <row r="106" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W106" s="7"/>
+    </row>
+    <row r="107" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W107" s="7"/>
+    </row>
+    <row r="108" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W108" s="7"/>
+    </row>
+    <row r="109" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W109" s="7"/>
+    </row>
+    <row r="110" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W110" s="7"/>
+    </row>
+    <row r="111" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W111" s="7"/>
+    </row>
+    <row r="112" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W112" s="7"/>
+    </row>
+    <row r="113" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W113" s="7"/>
+    </row>
+    <row r="114" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W114" s="7"/>
+    </row>
+    <row r="115" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W115" s="7"/>
+    </row>
+    <row r="116" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W116" s="7"/>
+    </row>
+    <row r="117" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W117" s="7"/>
+    </row>
+    <row r="118" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W118" s="7"/>
+    </row>
+    <row r="119" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W119" s="7"/>
+    </row>
+    <row r="120" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="W120" s="7"/>
+    </row>
+    <row r="121" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W121" s="7"/>
     </row>
-    <row r="122" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="122" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W122" s="7"/>
     </row>
-    <row r="123" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="123" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W123" s="7"/>
     </row>
-    <row r="124" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="124" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W124" s="7"/>
     </row>
-    <row r="125" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="125" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W125" s="7"/>
     </row>
-    <row r="126" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="126" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W126" s="7"/>
     </row>
-    <row r="127" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="127" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W127" s="7"/>
     </row>
-    <row r="128" spans="6:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+    <row r="128" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W128" s="7"/>
     </row>
     <row r="129" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -7327,142 +6663,13 @@
     <row r="494" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="W494" s="7"/>
     </row>
-    <row r="495" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W495" s="7"/>
-    </row>
-    <row r="496" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W496" s="7"/>
-    </row>
-    <row r="497" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W497" s="7"/>
-    </row>
-    <row r="498" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W498" s="7"/>
-    </row>
-    <row r="499" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W499" s="7"/>
-    </row>
-    <row r="500" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W500" s="7"/>
-    </row>
-    <row r="501" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W501" s="7"/>
-    </row>
-    <row r="502" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W502" s="7"/>
-    </row>
-    <row r="503" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W503" s="7"/>
-    </row>
-    <row r="504" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W504" s="7"/>
-    </row>
-    <row r="505" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W505" s="7"/>
-    </row>
-    <row r="506" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W506" s="7"/>
-    </row>
-    <row r="507" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W507" s="7"/>
-    </row>
-    <row r="508" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W508" s="7"/>
-    </row>
-    <row r="509" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W509" s="7"/>
-    </row>
-    <row r="510" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W510" s="7"/>
-    </row>
-    <row r="511" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W511" s="7"/>
-    </row>
-    <row r="512" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W512" s="7"/>
-    </row>
-    <row r="513" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W513" s="7"/>
-    </row>
-    <row r="514" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W514" s="7"/>
-    </row>
-    <row r="515" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W515" s="7"/>
-    </row>
-    <row r="516" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W516" s="7"/>
-    </row>
-    <row r="517" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W517" s="7"/>
-    </row>
-    <row r="518" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W518" s="7"/>
-    </row>
-    <row r="519" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W519" s="7"/>
-    </row>
-    <row r="520" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W520" s="7"/>
-    </row>
-    <row r="521" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W521" s="7"/>
-    </row>
-    <row r="522" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W522" s="7"/>
-    </row>
-    <row r="523" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W523" s="7"/>
-    </row>
-    <row r="524" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W524" s="7"/>
-    </row>
-    <row r="525" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W525" s="7"/>
-    </row>
-    <row r="526" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W526" s="7"/>
-    </row>
-    <row r="527" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W527" s="7"/>
-    </row>
-    <row r="528" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W528" s="7"/>
-    </row>
-    <row r="529" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W529" s="7"/>
-    </row>
-    <row r="530" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W530" s="7"/>
-    </row>
-    <row r="531" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W531" s="7"/>
-    </row>
-    <row r="532" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W532" s="7"/>
-    </row>
-    <row r="533" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W533" s="7"/>
-    </row>
-    <row r="534" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W534" s="7"/>
-    </row>
-    <row r="535" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W535" s="7"/>
-    </row>
-    <row r="536" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W536" s="7"/>
-    </row>
-    <row r="537" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="W537" s="7"/>
-    </row>
-    <row r="538" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="539" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="540" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="541" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="542" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="495" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="496" spans="23:23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="497" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="498" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="499" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A9:W34" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
+  <autoFilter ref="A9:W31" xr:uid="{00000000-0001-0000-0200-000000000000}"/>
   <mergeCells count="7">
     <mergeCell ref="A6:B6"/>
     <mergeCell ref="A2:B2"/>
@@ -7483,19 +6690,19 @@
           <x14:formula1>
             <xm:f>Sheet1!$B$2:$B$3</xm:f>
           </x14:formula1>
-          <xm:sqref>M10:N34 J10:J34 P10:R34</xm:sqref>
+          <xm:sqref>M10:N31 P10:R31 J10:J31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showErrorMessage="1" xr:uid="{70793024-27E9-4E6A-BACD-083AB683BC38}">
           <x14:formula1>
             <xm:f>Sheet1!$A$2:$A$3</xm:f>
           </x14:formula1>
-          <xm:sqref>T10:T34</xm:sqref>
+          <xm:sqref>T10:T31</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" xr:uid="{3DE61C5E-9DA3-4CE3-A1FF-8FBE651EA6B5}">
           <x14:formula1>
             <xm:f>'LISTA VALORI'!$A$2:$A$8</xm:f>
           </x14:formula1>
-          <xm:sqref>K10:K34</xm:sqref>
+          <xm:sqref>K10:K31</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -7510,42 +6717,42 @@
   <sheetData>
     <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
     </row>
     <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
     </row>
     <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
     </row>
   </sheetData>
@@ -7555,11 +6762,10 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
-  <sheetPr filterMode="1"/>
   <dimension ref="A1:G960"/>
   <sheetFormatPr defaultColWidth="14.42578125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16" style="15" customWidth="1"/>
+    <col min="1" max="1" width="16" style="13" customWidth="1"/>
     <col min="2" max="2" width="23.85546875" customWidth="1"/>
     <col min="3" max="3" width="33.85546875" customWidth="1"/>
     <col min="4" max="4" width="102" customWidth="1"/>
@@ -7569,238 +6775,264 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="14.25" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A1" s="28" t="s">
+      <c r="A1" s="26" t="s">
+        <v>111</v>
+      </c>
+      <c r="B1" s="11" t="s">
+        <v>20</v>
+      </c>
+      <c r="C1" s="11" t="s">
         <v>112</v>
       </c>
-      <c r="B1" s="11" t="s">
-        <v>21</v>
-      </c>
-      <c r="C1" s="11" t="s">
+      <c r="D1" s="40" t="s">
         <v>113</v>
       </c>
-      <c r="D1" s="11" t="s">
+      <c r="F1" s="12" t="s">
         <v>114</v>
       </c>
-      <c r="F1" s="14" t="s">
+      <c r="G1" s="36" t="s">
+        <v>147</v>
+      </c>
+    </row>
+    <row r="2" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A2" s="5" t="s">
+        <v>43</v>
+      </c>
+      <c r="B2" s="5" t="s">
         <v>115</v>
       </c>
-      <c r="G1" s="43" t="s">
+      <c r="C2" s="38" t="s">
         <v>116</v>
       </c>
-    </row>
-    <row r="2" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
-        <v>44</v>
-      </c>
-      <c r="B2" s="5" t="s">
+      <c r="D2" s="41" t="s">
         <v>117</v>
       </c>
-      <c r="C2" s="12" t="s">
+    </row>
+    <row r="3" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A3" s="5" t="s">
+        <v>47</v>
+      </c>
+      <c r="B3" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C3" s="38" t="s">
         <v>118</v>
       </c>
-      <c r="D2" s="29" t="s">
+      <c r="D3" s="42" t="s">
         <v>119</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
-        <v>48</v>
-      </c>
-      <c r="B3" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C3" s="12" t="s">
+    <row r="4" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A4" s="5" t="s">
+        <v>50</v>
+      </c>
+      <c r="B4" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C4" s="38" t="s">
         <v>120</v>
       </c>
-      <c r="D3" s="29" t="s">
+      <c r="D4" s="43" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="4" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="5" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A5" s="5" t="s">
+        <v>52</v>
+      </c>
+      <c r="B5" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C5" s="38" t="s">
+        <v>122</v>
+      </c>
+      <c r="D5" s="42" t="s">
+        <v>123</v>
+      </c>
+    </row>
+    <row r="6" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A6" s="5" t="s">
+        <v>53</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C6" s="38" t="s">
+        <v>124</v>
+      </c>
+      <c r="D6" s="43" t="s">
+        <v>125</v>
+      </c>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A7" s="5" t="s">
+        <v>54</v>
+      </c>
+      <c r="B7" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C7" s="38" t="s">
+        <v>126</v>
+      </c>
+      <c r="D7" s="43" t="s">
+        <v>127</v>
+      </c>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
+      <c r="A8" s="5" t="s">
         <v>51</v>
       </c>
-      <c r="B4" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C4" s="12" t="s">
-        <v>122</v>
-      </c>
-      <c r="D4" s="30" t="s">
-        <v>123</v>
-      </c>
-    </row>
-    <row r="5" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
-        <v>53</v>
-      </c>
-      <c r="B5" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C5" s="12" t="s">
-        <v>124</v>
-      </c>
-      <c r="D5" s="29" t="s">
-        <v>125</v>
-      </c>
-    </row>
-    <row r="6" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="5" t="s">
-        <v>54</v>
-      </c>
-      <c r="B6" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C6" s="12" t="s">
-        <v>126</v>
-      </c>
-      <c r="D6" s="30" t="s">
-        <v>127</v>
-      </c>
-    </row>
-    <row r="7" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="5" t="s">
-        <v>55</v>
-      </c>
-      <c r="B7" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C7" s="12" t="s">
+      <c r="B8" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C8" s="38" t="s">
         <v>128</v>
       </c>
-      <c r="D7" s="30" t="s">
+      <c r="D8" s="43" t="s">
         <v>129</v>
-      </c>
-    </row>
-    <row r="8" spans="1:7" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A8" s="5" t="s">
-        <v>52</v>
-      </c>
-      <c r="B8" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C8" s="12" t="s">
-        <v>130</v>
-      </c>
-      <c r="D8" s="30" t="s">
-        <v>131</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="B9" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C9" s="12" t="s">
+        <v>115</v>
+      </c>
+      <c r="C9" s="38" t="s">
+        <v>130</v>
+      </c>
+      <c r="D9" s="43" t="s">
+        <v>131</v>
+      </c>
+    </row>
+    <row r="10" spans="1:7" ht="45" x14ac:dyDescent="0.25">
+      <c r="A10" s="5" t="s">
         <v>132</v>
       </c>
-      <c r="D9" s="30" t="s">
+      <c r="B10" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C10" s="39" t="s">
         <v>133</v>
       </c>
-    </row>
-    <row r="10" spans="1:7" ht="45" hidden="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="5" t="s">
+      <c r="D10" s="42" t="s">
         <v>134</v>
       </c>
-      <c r="B10" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C10" s="13" t="s">
+    </row>
+    <row r="11" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A11" s="5" t="s">
+        <v>90</v>
+      </c>
+      <c r="B11" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C11" s="38" t="s">
         <v>135</v>
       </c>
-      <c r="D10" s="29" t="s">
+      <c r="D11" s="43" t="s">
         <v>136</v>
       </c>
     </row>
-    <row r="11" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A11" s="5" t="s">
-        <v>91</v>
-      </c>
-      <c r="B11" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C11" s="12" t="s">
+    <row r="12" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A12" s="5" t="s">
+        <v>99</v>
+      </c>
+      <c r="B12" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C12" s="38" t="s">
         <v>137</v>
       </c>
-      <c r="D11" s="30" t="s">
+      <c r="D12" s="43" t="s">
         <v>138</v>
       </c>
     </row>
-    <row r="12" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A12" s="5" t="s">
+    <row r="13" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A13" s="5" t="s">
         <v>100</v>
       </c>
-      <c r="B12" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C12" s="12" t="s">
+      <c r="B13" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C13" s="38" t="s">
         <v>139</v>
       </c>
-      <c r="D12" s="30" t="s">
+      <c r="D13" s="43" t="s">
         <v>140</v>
       </c>
     </row>
-    <row r="13" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A13" s="5" t="s">
+    <row r="14" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A14" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="B13" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C13" s="12" t="s">
+      <c r="B14" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C14" s="38" t="s">
         <v>141</v>
       </c>
-      <c r="D13" s="30" t="s">
+      <c r="D14" s="43" t="s">
         <v>142</v>
       </c>
     </row>
-    <row r="14" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A14" s="5" t="s">
+    <row r="15" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A15" s="5" t="s">
         <v>102</v>
       </c>
-      <c r="B14" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C14" s="12" t="s">
+      <c r="B15" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C15" s="38">
+        <v>521</v>
+      </c>
+      <c r="D15" s="43" t="s">
         <v>143</v>
       </c>
-      <c r="D14" s="30" t="s">
-        <v>144</v>
-      </c>
-    </row>
-    <row r="15" spans="1:7" ht="14.25" hidden="1" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A15" s="5" t="s">
-        <v>103</v>
-      </c>
-      <c r="B15" s="5" t="s">
-        <v>117</v>
-      </c>
-      <c r="C15" s="12">
-        <v>521</v>
-      </c>
-      <c r="D15" s="30" t="s">
-        <v>145</v>
-      </c>
-    </row>
-    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="17" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="18" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="19" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="20" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="21" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="22" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="23" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="24" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="25" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="26" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="27" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="28" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="29" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="30" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="31" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
-    <row r="32" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    </row>
+    <row r="16" spans="1:7" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A16" s="45" t="s">
+        <v>148</v>
+      </c>
+      <c r="B16" s="5" t="s">
+        <v>115</v>
+      </c>
+      <c r="C16" s="47" t="s">
+        <v>153</v>
+      </c>
+      <c r="D16" s="43" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="17" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A17" s="46" t="s">
+        <v>150</v>
+      </c>
+      <c r="B17" s="44" t="s">
+        <v>115</v>
+      </c>
+      <c r="C17" s="48" t="s">
+        <v>152</v>
+      </c>
+      <c r="D17" s="43" t="s">
+        <v>151</v>
+      </c>
+    </row>
+    <row r="18" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="19" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="20" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="21" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="22" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="23" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="24" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="25" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="26" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="27" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="28" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="29" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="30" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="31" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
+    <row r="32" spans="1:4" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="33" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="34" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="35" ht="14.25" customHeight="1" x14ac:dyDescent="0.25"/>
@@ -8730,13 +7962,7 @@
     <row r="959" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
     <row r="960" ht="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   </sheetData>
-  <autoFilter ref="A1:G15" xr:uid="{00000000-0001-0000-0300-000000000000}">
-    <filterColumn colId="0">
-      <filters>
-        <filter val="PSS"/>
-      </filters>
-    </filterColumn>
-  </autoFilter>
+  <autoFilter ref="A1:G10" xr:uid="{00000000-0001-0000-0300-000000000000}"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0" footer="0"/>
   <pageSetup orientation="landscape"/>
 </worksheet>
@@ -8754,26 +7980,26 @@
   <sheetData>
     <row r="1" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A1" s="4" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="B1" s="4" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="2" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="B2" s="4" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="3" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B3" s="4" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
     </row>
     <row r="4" spans="1:2" ht="14.25" customHeight="1" x14ac:dyDescent="0.25">
@@ -9787,15 +9013,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -10063,33 +9286,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{8C578C2C-7E0B-429D-96B0-25A2E02D9084}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
@@ -10108,9 +9325,18 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simone\Desktop\Accreditamento CVPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FD670DA3-26F7-4D87-9ED6-A96227AF2ECA}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DBF152-CE48-4D72-95BF-EF10DA7E0197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="208">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="206">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -742,9 +742,6 @@
     <t>Trattandosi di un potenziale errore di configurazione del sistema; serve un intervento tecnico manuale per correggere la configurazione e ripristinare il corretto funzionamento del servizio. Non Ã¨ possibile implementare un meccanismo automatico di retry o di invio manuale da parte dell'operatore; in quanto non essendo un errore transitorio; Ã¨ necessario intervenire sulla configurazione del sistema per risolverlo.</t>
   </si>
   <si>
-    <t>Campo valorizzato in modo fisso nel nell'invocazione del servizio</t>
-  </si>
-  <si>
     <t>Si valutano da backoffice le cause del timeout e si procede con intervento risolutivo. Successivamente il client puÃ² procedere con un nuovo tentantivo di invio del documento</t>
   </si>
   <si>
@@ -800,9 +797,6 @@
   </si>
   <si>
     <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.a324eae800^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>Campo valorizzato in modo fisso nel CDA</t>
   </si>
   <si>
     <t>0d2f7fa83f24c4e516b4012bf6460b66</t>
@@ -3030,7 +3024,7 @@
       </c>
       <c r="B2" s="52"/>
       <c r="C2" s="53" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D2" s="52"/>
       <c r="F2" s="6"/>
@@ -3058,7 +3052,7 @@
       </c>
       <c r="B3" s="55"/>
       <c r="C3" s="60" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D3" s="52"/>
       <c r="F3" s="6"/>
@@ -3084,7 +3078,7 @@
       <c r="A4" s="56"/>
       <c r="B4" s="57"/>
       <c r="C4" s="60" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="D4" s="52"/>
       <c r="E4" s="4"/>
@@ -3111,7 +3105,7 @@
       <c r="A5" s="58"/>
       <c r="B5" s="59"/>
       <c r="C5" s="60" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D5" s="52"/>
       <c r="F5" s="6"/>
@@ -3357,7 +3351,7 @@
         <v>146</v>
       </c>
       <c r="K11" s="29" t="s">
-        <v>161</v>
+        <v>106</v>
       </c>
       <c r="L11" s="29"/>
       <c r="M11" s="29"/>
@@ -3420,7 +3414,7 @@
         <v>146</v>
       </c>
       <c r="S12" s="29" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="T12" s="29"/>
       <c r="U12" s="30"/>
@@ -3449,10 +3443,10 @@
         <v>46101</v>
       </c>
       <c r="G13" s="28" t="s">
+        <v>162</v>
+      </c>
+      <c r="H13" s="28" t="s">
         <v>163</v>
-      </c>
-      <c r="H13" s="28" t="s">
-        <v>164</v>
       </c>
       <c r="I13" s="33" t="s">
         <v>157</v>
@@ -3481,7 +3475,7 @@
         <v>58</v>
       </c>
       <c r="S13" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T13" s="29"/>
       <c r="U13" s="30"/>
@@ -3510,13 +3504,13 @@
         <v>46101</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="H14" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="I14" s="33" t="s">
         <v>166</v>
-      </c>
-      <c r="I14" s="33" t="s">
-        <v>167</v>
       </c>
       <c r="J14" s="29" t="s">
         <v>58</v>
@@ -3542,7 +3536,7 @@
         <v>58</v>
       </c>
       <c r="S14" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T14" s="29"/>
       <c r="U14" s="30"/>
@@ -3571,13 +3565,13 @@
         <v>46101</v>
       </c>
       <c r="G15" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="H15" s="28" t="s">
         <v>168</v>
       </c>
-      <c r="H15" s="28" t="s">
+      <c r="I15" s="33" t="s">
         <v>169</v>
-      </c>
-      <c r="I15" s="33" t="s">
-        <v>170</v>
       </c>
       <c r="J15" s="29" t="s">
         <v>58</v>
@@ -3603,7 +3597,7 @@
         <v>58</v>
       </c>
       <c r="S15" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T15" s="29"/>
       <c r="U15" s="30"/>
@@ -3632,13 +3626,13 @@
         <v>46101</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="H16" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="I16" s="33" t="s">
         <v>171</v>
-      </c>
-      <c r="I16" s="33" t="s">
-        <v>172</v>
       </c>
       <c r="J16" s="29" t="s">
         <v>58</v>
@@ -3664,7 +3658,7 @@
         <v>58</v>
       </c>
       <c r="S16" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T16" s="29"/>
       <c r="U16" s="30"/>
@@ -3693,13 +3687,13 @@
         <v>46101</v>
       </c>
       <c r="G17" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="H17" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="H17" s="28" t="s">
+      <c r="I17" s="33" t="s">
         <v>174</v>
-      </c>
-      <c r="I17" s="33" t="s">
-        <v>175</v>
       </c>
       <c r="J17" s="29" t="s">
         <v>58</v>
@@ -3725,7 +3719,7 @@
         <v>58</v>
       </c>
       <c r="S17" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T17" s="29"/>
       <c r="U17" s="30"/>
@@ -3754,13 +3748,13 @@
         <v>46101</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="H18" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="I18" s="33" t="s">
         <v>176</v>
-      </c>
-      <c r="I18" s="33" t="s">
-        <v>177</v>
       </c>
       <c r="J18" s="29" t="s">
         <v>58</v>
@@ -3786,7 +3780,7 @@
         <v>58</v>
       </c>
       <c r="S18" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T18" s="29"/>
       <c r="U18" s="30"/>
@@ -3815,13 +3809,13 @@
         <v>46101</v>
       </c>
       <c r="G19" s="28" t="s">
+        <v>177</v>
+      </c>
+      <c r="H19" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="H19" s="28" t="s">
+      <c r="I19" s="33" t="s">
         <v>179</v>
-      </c>
-      <c r="I19" s="33" t="s">
-        <v>180</v>
       </c>
       <c r="J19" s="29" t="s">
         <v>58</v>
@@ -3847,7 +3841,7 @@
         <v>58</v>
       </c>
       <c r="S19" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T19" s="29"/>
       <c r="U19" s="30"/>
@@ -3880,7 +3874,7 @@
         <v>146</v>
       </c>
       <c r="K20" s="29" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="L20" s="29"/>
       <c r="M20" s="29"/>
@@ -3919,13 +3913,13 @@
         <v>46101</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="J21" s="29" t="s">
         <v>58</v>
@@ -3951,7 +3945,7 @@
         <v>58</v>
       </c>
       <c r="S21" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T21" s="29"/>
       <c r="U21" s="30"/>
@@ -3980,13 +3974,13 @@
         <v>46101</v>
       </c>
       <c r="G22" s="28" t="s">
+        <v>182</v>
+      </c>
+      <c r="H22" s="28" t="s">
+        <v>183</v>
+      </c>
+      <c r="I22" s="33" t="s">
         <v>184</v>
-      </c>
-      <c r="H22" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="I22" s="33" t="s">
-        <v>186</v>
       </c>
       <c r="J22" s="29" t="s">
         <v>58</v>
@@ -4012,7 +4006,7 @@
         <v>58</v>
       </c>
       <c r="S22" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T22" s="29"/>
       <c r="U22" s="30"/>
@@ -4041,13 +4035,13 @@
         <v>46101</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="J23" s="29" t="s">
         <v>58</v>
@@ -4073,7 +4067,7 @@
         <v>58</v>
       </c>
       <c r="S23" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T23" s="29"/>
       <c r="U23" s="30"/>
@@ -4102,13 +4096,13 @@
         <v>46101</v>
       </c>
       <c r="G24" s="28" t="s">
+        <v>187</v>
+      </c>
+      <c r="H24" s="28" t="s">
+        <v>188</v>
+      </c>
+      <c r="I24" s="33" t="s">
         <v>189</v>
-      </c>
-      <c r="H24" s="28" t="s">
-        <v>190</v>
-      </c>
-      <c r="I24" s="33" t="s">
-        <v>191</v>
       </c>
       <c r="J24" s="29" t="s">
         <v>58</v>
@@ -4134,7 +4128,7 @@
         <v>58</v>
       </c>
       <c r="S24" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T24" s="29"/>
       <c r="U24" s="30"/>
@@ -4163,13 +4157,13 @@
         <v>46101</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="I25" s="33" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="J25" s="29" t="s">
         <v>58</v>
@@ -4195,7 +4189,7 @@
         <v>58</v>
       </c>
       <c r="S25" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T25" s="29"/>
       <c r="U25" s="30"/>
@@ -4224,13 +4218,13 @@
         <v>46101</v>
       </c>
       <c r="G26" s="28" t="s">
+        <v>192</v>
+      </c>
+      <c r="H26" s="28" t="s">
+        <v>193</v>
+      </c>
+      <c r="I26" s="33" t="s">
         <v>194</v>
-      </c>
-      <c r="H26" s="28" t="s">
-        <v>195</v>
-      </c>
-      <c r="I26" s="33" t="s">
-        <v>196</v>
       </c>
       <c r="J26" s="29" t="s">
         <v>58</v>
@@ -4256,7 +4250,7 @@
         <v>58</v>
       </c>
       <c r="S26" s="29" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="T26" s="29"/>
       <c r="U26" s="30"/>
@@ -4289,7 +4283,7 @@
         <v>146</v>
       </c>
       <c r="K27" s="29" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="L27" s="29"/>
       <c r="M27" s="29"/>
@@ -4332,7 +4326,7 @@
         <v>146</v>
       </c>
       <c r="K28" s="29" t="s">
-        <v>181</v>
+        <v>106</v>
       </c>
       <c r="L28" s="27"/>
       <c r="M28" s="29"/>
@@ -4371,13 +4365,13 @@
         <v>46101</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="H29" s="28" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="J29" s="29" t="s">
         <v>58</v>
@@ -4418,13 +4412,13 @@
         <v>46101</v>
       </c>
       <c r="G30" s="28" t="s">
+        <v>197</v>
+      </c>
+      <c r="H30" s="28" t="s">
+        <v>198</v>
+      </c>
+      <c r="I30" s="33" t="s">
         <v>199</v>
-      </c>
-      <c r="H30" s="28" t="s">
-        <v>200</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>201</v>
       </c>
       <c r="J30" s="29" t="s">
         <v>58</v>
@@ -4465,13 +4459,13 @@
         <v>46101</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H31" s="28" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="I31" s="33" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="J31" s="29" t="s">
         <v>58</v>
@@ -9013,12 +9007,15 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -9286,21 +9283,27 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9325,18 +9328,9 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>

--- a/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simone\Desktop\Accreditamento CVPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F1DBF152-CE48-4D72-95BF-EF10DA7E0197}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9935F2D6-EDFC-4B8B-BF7A-E02CEF4D1E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="600" windowWidth="19440" windowHeight="14880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Istruzioni Compilazione" sheetId="1" r:id="rId1"/>
@@ -80,7 +80,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="206">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="207">
   <si>
     <t>COME VALORIZZARE LA CHECKLIST (tab TestCases)</t>
   </si>
@@ -724,12 +724,6 @@
 *) Il test in questione è da intendersi obbligatorio per gli applicativi che si stanno accreditando per la prima volta per PSS; nel caso di applicativi già accreditati, sarà sufficiente sottomettere il caso di test 478 (Fast Track)</t>
   </si>
   <si>
-    <t>2026-03-20T10:09:54Z</t>
-  </si>
-  <si>
-    <t>39702757cddab418e5fe7ac8c1d75f80</t>
-  </si>
-  <si>
     <t>UNKNOWN_WORKFLOW_ID</t>
   </si>
   <si>
@@ -739,132 +733,12 @@
     <t>Si valutano da backoffice le cause dell'errore e si procede con intervento risolutivo. Successivamente il client puÃ² procedere con un nuovo tentantivo di invio del documento</t>
   </si>
   <si>
-    <t>Trattandosi di un potenziale errore di configurazione del sistema; serve un intervento tecnico manuale per correggere la configurazione e ripristinare il corretto funzionamento del servizio. Non Ã¨ possibile implementare un meccanismo automatico di retry o di invio manuale da parte dell'operatore; in quanto non essendo un errore transitorio; Ã¨ necessario intervenire sulla configurazione del sistema per risolverlo.</t>
-  </si>
-  <si>
     <t>Si valutano da backoffice le cause del timeout e si procede con intervento risolutivo. Successivamente il client puÃ² procedere con un nuovo tentantivo di invio del documento</t>
   </si>
   <si>
-    <t>2026-03-20T10:09:55Z</t>
-  </si>
-  <si>
-    <t>603b75fa8547fcf792f1beadedcc62f1</t>
-  </si>
-  <si>
     <t>Si chiede al client di completare correttamente i dati mancanti obbligatori (o errati) e successivamente si puÃ² procedere ad un reinvio.</t>
   </si>
   <si>
-    <t>163ae4772447a0e77d149796464ce89a</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.e135ecd10b^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:56Z</t>
-  </si>
-  <si>
-    <t>2e4980c8d3e814320516b9be0baf2ed5</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.29ef461ea1^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>96dc0c142ed75fdfdc3397468d5a9b6c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.67ede4d03e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:57Z</t>
-  </si>
-  <si>
-    <t>0e9048efec64209ff40f88ee405b0c76</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.e0ade7d43e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>0e226372d630b7d3f82651b7f2fd84f0</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.f73b7ff4d9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:58Z</t>
-  </si>
-  <si>
-    <t>29f42e00adc64e66f3379bfd537dd4e4</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.a324eae800^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>0d2f7fa83f24c4e516b4012bf6460b66</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.61a0edf737^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:09:59Z</t>
-  </si>
-  <si>
-    <t>f7c262c458e153dd67a2cc2a4d4dda8c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.bd6aef7f3f^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>e1ecf46385f94322dd6da587e9ed2346</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.94dedb6589^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:10:00Z</t>
-  </si>
-  <si>
-    <t>e6b8e8505b938952d043a9aa31d74a60</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.f62c0cb56d^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>ecd4eab87931f713807544556bb41a43</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b1ccb8d477^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:10:01Z</t>
-  </si>
-  <si>
-    <t>11ddd03d938d38e9526ef023e615a500</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.38606f276c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>47ef248ec4fcb09a146904313149721f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.ae940dd255^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-03-20T10:10:02Z</t>
-  </si>
-  <si>
-    <t>4da0ddb5ecaf884682eb7eae6e9d2955</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9312649e23^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>75414d9618f747ef2f319b39d2a5cc41</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9935227025^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
     <t>subject_application_id: Lepida_CVPI</t>
   </si>
   <si>
@@ -875,6 +749,135 @@
   </si>
   <si>
     <t>Lepida</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:39Z</t>
+  </si>
+  <si>
+    <t>786ffd10c881f93119910ed6191f3b6b</t>
+  </si>
+  <si>
+    <t>Trattandosi di un potenziale errore di configurazione del sistema, serve un intervento tecnico manuale per correggere la configurazione e ripristinare il corretto funzionamento del servizio. Non Ã¨ possibile implementare un meccanismo automatico di retry o di invio manuale da parte dell'operatore, in quanto non essendo un errore transitorio, Ã¨ necessario intervenire sulla configurazione del sistema per risolverlo.</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:40Z</t>
+  </si>
+  <si>
+    <t>ee289fab8dae98ba3ff5f01871749908</t>
+  </si>
+  <si>
+    <t>e7f70f6aa3d4363d260c3c640cf3c88d</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b31a55bec2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:41Z</t>
+  </si>
+  <si>
+    <t>ba1aca2abb0a6c8c1cf6d4432440a38b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.3cf04f564e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>d62eed1f28d0c22b593111e1b30f4218</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.279953b1ea^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:42Z</t>
+  </si>
+  <si>
+    <t>ec593b225702d7a59512c0fbf665ce09</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.1b6fa7f13c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>5fa6f6406a3abc7682735d8352b2d538</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.7b162f22b0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:43Z</t>
+  </si>
+  <si>
+    <t>72361002de82a1d64317a4dce9499d3e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.8d4f01f30e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>9996e6c751d86b6381877afc50e029ca</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.1275ce2518^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:44Z</t>
+  </si>
+  <si>
+    <t>22e25dfe6a76770ed1e75579626e9b99</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9d8d935530^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>e69048f4fd647be970dcb6631e61c294</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b0257dd571^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:45Z</t>
+  </si>
+  <si>
+    <t>5a4766c5cb459fdc576191be2f54bf5c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.82ad7ed288^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:46Z</t>
+  </si>
+  <si>
+    <t>421f6bafa6354df045cb69a7297aa205</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.60a11b925c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>fa0b267ca0d06a72f77d245ee36e3152</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.203ceb09f0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:47Z</t>
+  </si>
+  <si>
+    <t>d0227eb5d117eeed60cf16f8d68d665f</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.0a41b84744^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-07T18:40:48Z</t>
+  </si>
+  <si>
+    <t>52dbedf7e13bf57e1592f39428fbf70b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b55e65c1ff^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>1cfb772407c14c80471c859ce07a6fe6</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.0ea71b482c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -3024,7 +3027,7 @@
       </c>
       <c r="B2" s="52"/>
       <c r="C2" s="53" t="s">
-        <v>205</v>
+        <v>163</v>
       </c>
       <c r="D2" s="52"/>
       <c r="F2" s="6"/>
@@ -3052,7 +3055,7 @@
       </c>
       <c r="B3" s="55"/>
       <c r="C3" s="60" t="s">
-        <v>202</v>
+        <v>160</v>
       </c>
       <c r="D3" s="52"/>
       <c r="F3" s="6"/>
@@ -3078,7 +3081,7 @@
       <c r="A4" s="56"/>
       <c r="B4" s="57"/>
       <c r="C4" s="60" t="s">
-        <v>203</v>
+        <v>161</v>
       </c>
       <c r="D4" s="52"/>
       <c r="E4" s="4"/>
@@ -3105,7 +3108,7 @@
       <c r="A5" s="58"/>
       <c r="B5" s="59"/>
       <c r="C5" s="60" t="s">
-        <v>204</v>
+        <v>162</v>
       </c>
       <c r="D5" s="52"/>
       <c r="F5" s="6"/>
@@ -3281,16 +3284,16 @@
         <v>45</v>
       </c>
       <c r="F10" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G10" s="28" t="s">
+        <v>164</v>
+      </c>
+      <c r="H10" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="I10" s="33" t="s">
         <v>155</v>
-      </c>
-      <c r="H10" s="28" t="s">
-        <v>156</v>
-      </c>
-      <c r="I10" s="33" t="s">
-        <v>157</v>
       </c>
       <c r="J10" s="29" t="s">
         <v>58</v>
@@ -3304,7 +3307,7 @@
         <v>58</v>
       </c>
       <c r="O10" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P10" s="29" t="s">
         <v>58</v>
@@ -3316,12 +3319,12 @@
         <v>146</v>
       </c>
       <c r="S10" s="29" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="T10" s="29"/>
       <c r="U10" s="30"/>
       <c r="V10" s="31" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="W10" s="29" t="s">
         <v>46</v>
@@ -3402,7 +3405,7 @@
         <v>58</v>
       </c>
       <c r="O12" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P12" s="29" t="s">
         <v>58</v>
@@ -3414,7 +3417,7 @@
         <v>146</v>
       </c>
       <c r="S12" s="29" t="s">
-        <v>161</v>
+        <v>158</v>
       </c>
       <c r="T12" s="29"/>
       <c r="U12" s="30"/>
@@ -3440,16 +3443,16 @@
         <v>61</v>
       </c>
       <c r="F13" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G13" s="28" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H13" s="28" t="s">
-        <v>163</v>
+        <v>168</v>
       </c>
       <c r="I13" s="33" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="J13" s="29" t="s">
         <v>58</v>
@@ -3463,7 +3466,7 @@
         <v>58</v>
       </c>
       <c r="O13" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P13" s="29" t="s">
         <v>58</v>
@@ -3475,7 +3478,7 @@
         <v>58</v>
       </c>
       <c r="S13" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T13" s="29"/>
       <c r="U13" s="30"/>
@@ -3501,16 +3504,16 @@
         <v>63</v>
       </c>
       <c r="F14" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G14" s="28" t="s">
-        <v>162</v>
+        <v>167</v>
       </c>
       <c r="H14" s="28" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="I14" s="33" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="J14" s="29" t="s">
         <v>58</v>
@@ -3524,7 +3527,7 @@
         <v>58</v>
       </c>
       <c r="O14" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P14" s="29" t="s">
         <v>58</v>
@@ -3536,7 +3539,7 @@
         <v>58</v>
       </c>
       <c r="S14" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T14" s="29"/>
       <c r="U14" s="30"/>
@@ -3562,16 +3565,16 @@
         <v>65</v>
       </c>
       <c r="F15" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G15" s="28" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H15" s="28" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="I15" s="33" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="J15" s="29" t="s">
         <v>58</v>
@@ -3585,7 +3588,7 @@
         <v>58</v>
       </c>
       <c r="O15" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P15" s="29" t="s">
         <v>58</v>
@@ -3597,7 +3600,7 @@
         <v>58</v>
       </c>
       <c r="S15" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T15" s="29"/>
       <c r="U15" s="30"/>
@@ -3623,16 +3626,16 @@
         <v>67</v>
       </c>
       <c r="F16" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G16" s="28" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="H16" s="28" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="I16" s="33" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="J16" s="29" t="s">
         <v>58</v>
@@ -3646,7 +3649,7 @@
         <v>58</v>
       </c>
       <c r="O16" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P16" s="29" t="s">
         <v>58</v>
@@ -3658,7 +3661,7 @@
         <v>58</v>
       </c>
       <c r="S16" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T16" s="29"/>
       <c r="U16" s="30"/>
@@ -3684,16 +3687,16 @@
         <v>69</v>
       </c>
       <c r="F17" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G17" s="28" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H17" s="28" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="I17" s="33" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="J17" s="29" t="s">
         <v>58</v>
@@ -3707,7 +3710,7 @@
         <v>58</v>
       </c>
       <c r="O17" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P17" s="29" t="s">
         <v>58</v>
@@ -3719,7 +3722,7 @@
         <v>58</v>
       </c>
       <c r="S17" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T17" s="29"/>
       <c r="U17" s="30"/>
@@ -3745,16 +3748,16 @@
         <v>71</v>
       </c>
       <c r="F18" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G18" s="28" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="H18" s="28" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="I18" s="33" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="J18" s="29" t="s">
         <v>58</v>
@@ -3768,7 +3771,7 @@
         <v>58</v>
       </c>
       <c r="O18" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P18" s="29" t="s">
         <v>58</v>
@@ -3780,7 +3783,7 @@
         <v>58</v>
       </c>
       <c r="S18" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T18" s="29"/>
       <c r="U18" s="30"/>
@@ -3806,16 +3809,16 @@
         <v>73</v>
       </c>
       <c r="F19" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G19" s="28" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H19" s="28" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="I19" s="33" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="J19" s="29" t="s">
         <v>58</v>
@@ -3829,7 +3832,7 @@
         <v>58</v>
       </c>
       <c r="O19" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P19" s="29" t="s">
         <v>58</v>
@@ -3841,7 +3844,7 @@
         <v>58</v>
       </c>
       <c r="S19" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T19" s="29"/>
       <c r="U19" s="30"/>
@@ -3910,16 +3913,16 @@
         <v>77</v>
       </c>
       <c r="F21" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G21" s="28" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="H21" s="28" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="I21" s="33" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="J21" s="29" t="s">
         <v>58</v>
@@ -3933,7 +3936,7 @@
         <v>58</v>
       </c>
       <c r="O21" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P21" s="29" t="s">
         <v>58</v>
@@ -3945,7 +3948,7 @@
         <v>58</v>
       </c>
       <c r="S21" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T21" s="29"/>
       <c r="U21" s="30"/>
@@ -3971,16 +3974,16 @@
         <v>79</v>
       </c>
       <c r="F22" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G22" s="28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H22" s="28" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="I22" s="33" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="J22" s="29" t="s">
         <v>58</v>
@@ -3994,7 +3997,7 @@
         <v>58</v>
       </c>
       <c r="O22" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P22" s="29" t="s">
         <v>58</v>
@@ -4006,7 +4009,7 @@
         <v>58</v>
       </c>
       <c r="S22" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T22" s="29"/>
       <c r="U22" s="30"/>
@@ -4032,16 +4035,16 @@
         <v>81</v>
       </c>
       <c r="F23" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G23" s="28" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="H23" s="28" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="I23" s="33" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="J23" s="29" t="s">
         <v>58</v>
@@ -4055,7 +4058,7 @@
         <v>58</v>
       </c>
       <c r="O23" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P23" s="29" t="s">
         <v>58</v>
@@ -4067,7 +4070,7 @@
         <v>58</v>
       </c>
       <c r="S23" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T23" s="29"/>
       <c r="U23" s="30"/>
@@ -4093,16 +4096,16 @@
         <v>83</v>
       </c>
       <c r="F24" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G24" s="28" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="H24" s="28" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="I24" s="33" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="J24" s="29" t="s">
         <v>58</v>
@@ -4116,7 +4119,7 @@
         <v>58</v>
       </c>
       <c r="O24" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P24" s="29" t="s">
         <v>58</v>
@@ -4128,7 +4131,7 @@
         <v>58</v>
       </c>
       <c r="S24" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T24" s="29"/>
       <c r="U24" s="30"/>
@@ -4154,16 +4157,16 @@
         <v>85</v>
       </c>
       <c r="F25" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G25" s="28" t="s">
-        <v>187</v>
+        <v>194</v>
       </c>
       <c r="H25" s="28" t="s">
-        <v>190</v>
+        <v>195</v>
       </c>
       <c r="I25" s="33" t="s">
-        <v>191</v>
+        <v>196</v>
       </c>
       <c r="J25" s="29" t="s">
         <v>58</v>
@@ -4177,7 +4180,7 @@
         <v>58</v>
       </c>
       <c r="O25" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P25" s="29" t="s">
         <v>58</v>
@@ -4189,7 +4192,7 @@
         <v>58</v>
       </c>
       <c r="S25" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T25" s="29"/>
       <c r="U25" s="30"/>
@@ -4215,16 +4218,16 @@
         <v>87</v>
       </c>
       <c r="F26" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>192</v>
+        <v>194</v>
       </c>
       <c r="H26" s="28" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="I26" s="33" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="J26" s="29" t="s">
         <v>58</v>
@@ -4238,7 +4241,7 @@
         <v>58</v>
       </c>
       <c r="O26" s="29" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="P26" s="29" t="s">
         <v>58</v>
@@ -4250,7 +4253,7 @@
         <v>58</v>
       </c>
       <c r="S26" s="29" t="s">
-        <v>164</v>
+        <v>159</v>
       </c>
       <c r="T26" s="29"/>
       <c r="U26" s="30"/>
@@ -4362,16 +4365,16 @@
         <v>94</v>
       </c>
       <c r="F29" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G29" s="28" t="s">
-        <v>192</v>
+        <v>199</v>
       </c>
       <c r="H29" s="28" t="s">
-        <v>195</v>
+        <v>200</v>
       </c>
       <c r="I29" s="33" t="s">
-        <v>196</v>
+        <v>201</v>
       </c>
       <c r="J29" s="29" t="s">
         <v>58</v>
@@ -4409,16 +4412,16 @@
         <v>96</v>
       </c>
       <c r="F30" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G30" s="28" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H30" s="28" t="s">
-        <v>198</v>
+        <v>203</v>
       </c>
       <c r="I30" s="33" t="s">
-        <v>199</v>
+        <v>204</v>
       </c>
       <c r="J30" s="29" t="s">
         <v>58</v>
@@ -4456,16 +4459,16 @@
         <v>98</v>
       </c>
       <c r="F31" s="28">
-        <v>46101</v>
+        <v>46119</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>197</v>
+        <v>202</v>
       </c>
       <c r="H31" s="28" t="s">
-        <v>200</v>
+        <v>205</v>
       </c>
       <c r="I31" s="33" t="s">
-        <v>201</v>
+        <v>206</v>
       </c>
       <c r="J31" s="29" t="s">
         <v>58</v>
@@ -9007,18 +9010,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -9282,6 +9273,18 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <?mso-contentType ?>
 <FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
@@ -9292,23 +9295,6 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
-  <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
-  </ds:schemaRefs>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
@@ -9327,6 +9313,23 @@
 </ds:datastoreItem>
 </file>
 
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{6C4C806F-EC4E-4231-9462-6D32094C4603}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/XML/1998/namespace"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>

--- a/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
+++ b/GATEWAY/A1#111080XXXXXXXX/Lepida/Lepida_CVPI/2.1.0/report-checklist.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Simone\Desktop\Accreditamento CVPI\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9935F2D6-EDFC-4B8B-BF7A-E02CEF4D1E1B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{17701A64-04F5-4C6F-98AA-288004F7CE69}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="28680" yWindow="600" windowWidth="19440" windowHeight="14880" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -751,133 +751,133 @@
     <t>Lepida</t>
   </si>
   <si>
-    <t>2026-04-07T18:40:39Z</t>
-  </si>
-  <si>
-    <t>786ffd10c881f93119910ed6191f3b6b</t>
-  </si>
-  <si>
     <t>Trattandosi di un potenziale errore di configurazione del sistema, serve un intervento tecnico manuale per correggere la configurazione e ripristinare il corretto funzionamento del servizio. Non Ã¨ possibile implementare un meccanismo automatico di retry o di invio manuale da parte dell'operatore, in quanto non essendo un errore transitorio, Ã¨ necessario intervenire sulla configurazione del sistema per risolverlo.</t>
   </si>
   <si>
-    <t>2026-04-07T18:40:40Z</t>
-  </si>
-  <si>
-    <t>ee289fab8dae98ba3ff5f01871749908</t>
-  </si>
-  <si>
-    <t>e7f70f6aa3d4363d260c3c640cf3c88d</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b31a55bec2^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:41Z</t>
-  </si>
-  <si>
-    <t>ba1aca2abb0a6c8c1cf6d4432440a38b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.3cf04f564e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>d62eed1f28d0c22b593111e1b30f4218</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.279953b1ea^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:42Z</t>
-  </si>
-  <si>
-    <t>ec593b225702d7a59512c0fbf665ce09</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.1b6fa7f13c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>5fa6f6406a3abc7682735d8352b2d538</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.7b162f22b0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:43Z</t>
-  </si>
-  <si>
-    <t>72361002de82a1d64317a4dce9499d3e</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.8d4f01f30e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>9996e6c751d86b6381877afc50e029ca</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.1275ce2518^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:44Z</t>
-  </si>
-  <si>
-    <t>22e25dfe6a76770ed1e75579626e9b99</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9d8d935530^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>e69048f4fd647be970dcb6631e61c294</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b0257dd571^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:45Z</t>
-  </si>
-  <si>
-    <t>5a4766c5cb459fdc576191be2f54bf5c</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.82ad7ed288^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:46Z</t>
-  </si>
-  <si>
-    <t>421f6bafa6354df045cb69a7297aa205</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.60a11b925c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>fa0b267ca0d06a72f77d245ee36e3152</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.203ceb09f0^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:47Z</t>
-  </si>
-  <si>
-    <t>d0227eb5d117eeed60cf16f8d68d665f</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.0a41b84744^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>2026-04-07T18:40:48Z</t>
-  </si>
-  <si>
-    <t>52dbedf7e13bf57e1592f39428fbf70b</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b55e65c1ff^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
-  </si>
-  <si>
-    <t>1cfb772407c14c80471c859ce07a6fe6</t>
-  </si>
-  <si>
-    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.0ea71b482c^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+    <t>2026-04-09T22:38:54Z</t>
+  </si>
+  <si>
+    <t>4c62e776cdc4ec9086c03ccf32de402d</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:38:55Z</t>
+  </si>
+  <si>
+    <t>2ef2431ac9cca36937386d391d1ab25e</t>
+  </si>
+  <si>
+    <t>e75a929fa0f61b00911036ecee8b3e98</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.455dcdbac9^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:38:56Z</t>
+  </si>
+  <si>
+    <t>d8521d903675718bf7a6f7abc8842fe2</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b25c4466a3^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>49d9d4633da579238a52321cd3287e65</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.94a5541612^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:38:57Z</t>
+  </si>
+  <si>
+    <t>f564df227aa906f617ced0a8373c9812</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.70729f8974^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>9a577290ce71f73cfd54d8779aa1db20</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.b655c1744e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:38:58Z</t>
+  </si>
+  <si>
+    <t>eb8c1bdbd23fd6526a666be0d6295958</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.9cb2e53a58^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>4f18b9c916c5c76d60a79b2153f942f9</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.bd21df7b8e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:38:59Z</t>
+  </si>
+  <si>
+    <t>6df8759b19cfbb261f68893e428d4ad1</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.3396c4435a^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>b65a49ab1da036bba9b5431f206d157b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.1653218b18^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:39:00Z</t>
+  </si>
+  <si>
+    <t>eaf05afdaaf73d9a6ef854d6f005296d</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.c38fa515fd^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>a41bf917c873952ceb7dc71d89c2d238</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.8b6d0e0dc7^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:39:01Z</t>
+  </si>
+  <si>
+    <t>f79a45babc9cd569e752a20b02f60ff7</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.8caee0747e^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>c93353317296979c2e017ed3b778e19c</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.73124c0259^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:39:02Z</t>
+  </si>
+  <si>
+    <t>5992211cef2f11da08cbe832276c486b</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.70fd3e2897^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
+  </si>
+  <si>
+    <t>2026-04-09T22:39:03Z</t>
+  </si>
+  <si>
+    <t>82a8b3f431e5fe5347b0ebe27b58db0e</t>
+  </si>
+  <si>
+    <t>2.16.840.1.113883.2.9.2.80.3.1.4.4.736173ee74d930e556d58b87162a2f32bc02383a123808d438ea8244bfa6a3b9.428362e872^^^^urn:ihe:iti:xdw:2013:workflowInstanceId</t>
   </si>
 </sst>
 </file>
@@ -3284,13 +3284,13 @@
         <v>45</v>
       </c>
       <c r="F10" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G10" s="28" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
       <c r="H10" s="28" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="I10" s="33" t="s">
         <v>155</v>
@@ -3324,7 +3324,7 @@
       <c r="T10" s="29"/>
       <c r="U10" s="30"/>
       <c r="V10" s="31" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="W10" s="29" t="s">
         <v>46</v>
@@ -3443,7 +3443,7 @@
         <v>61</v>
       </c>
       <c r="F13" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G13" s="28" t="s">
         <v>167</v>
@@ -3504,7 +3504,7 @@
         <v>63</v>
       </c>
       <c r="F14" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G14" s="28" t="s">
         <v>167</v>
@@ -3565,7 +3565,7 @@
         <v>65</v>
       </c>
       <c r="F15" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G15" s="28" t="s">
         <v>171</v>
@@ -3626,7 +3626,7 @@
         <v>67</v>
       </c>
       <c r="F16" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G16" s="28" t="s">
         <v>171</v>
@@ -3687,7 +3687,7 @@
         <v>69</v>
       </c>
       <c r="F17" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G17" s="28" t="s">
         <v>176</v>
@@ -3748,7 +3748,7 @@
         <v>71</v>
       </c>
       <c r="F18" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G18" s="28" t="s">
         <v>176</v>
@@ -3809,7 +3809,7 @@
         <v>73</v>
       </c>
       <c r="F19" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G19" s="28" t="s">
         <v>181</v>
@@ -3913,7 +3913,7 @@
         <v>77</v>
       </c>
       <c r="F21" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G21" s="28" t="s">
         <v>181</v>
@@ -3974,7 +3974,7 @@
         <v>79</v>
       </c>
       <c r="F22" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G22" s="28" t="s">
         <v>186</v>
@@ -4035,7 +4035,7 @@
         <v>81</v>
       </c>
       <c r="F23" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G23" s="28" t="s">
         <v>186</v>
@@ -4096,7 +4096,7 @@
         <v>83</v>
       </c>
       <c r="F24" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G24" s="28" t="s">
         <v>191</v>
@@ -4157,16 +4157,16 @@
         <v>85</v>
       </c>
       <c r="F25" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G25" s="28" t="s">
+        <v>191</v>
+      </c>
+      <c r="H25" s="28" t="s">
         <v>194</v>
       </c>
-      <c r="H25" s="28" t="s">
+      <c r="I25" s="33" t="s">
         <v>195</v>
-      </c>
-      <c r="I25" s="33" t="s">
-        <v>196</v>
       </c>
       <c r="J25" s="29" t="s">
         <v>58</v>
@@ -4218,10 +4218,10 @@
         <v>87</v>
       </c>
       <c r="F26" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G26" s="28" t="s">
-        <v>194</v>
+        <v>196</v>
       </c>
       <c r="H26" s="28" t="s">
         <v>197</v>
@@ -4365,16 +4365,16 @@
         <v>94</v>
       </c>
       <c r="F29" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G29" s="28" t="s">
+        <v>196</v>
+      </c>
+      <c r="H29" s="28" t="s">
         <v>199</v>
       </c>
-      <c r="H29" s="28" t="s">
+      <c r="I29" s="33" t="s">
         <v>200</v>
-      </c>
-      <c r="I29" s="33" t="s">
-        <v>201</v>
       </c>
       <c r="J29" s="29" t="s">
         <v>58</v>
@@ -4412,16 +4412,16 @@
         <v>96</v>
       </c>
       <c r="F30" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G30" s="28" t="s">
+        <v>201</v>
+      </c>
+      <c r="H30" s="28" t="s">
         <v>202</v>
       </c>
-      <c r="H30" s="28" t="s">
+      <c r="I30" s="33" t="s">
         <v>203</v>
-      </c>
-      <c r="I30" s="33" t="s">
-        <v>204</v>
       </c>
       <c r="J30" s="29" t="s">
         <v>58</v>
@@ -4459,10 +4459,10 @@
         <v>98</v>
       </c>
       <c r="F31" s="28">
-        <v>46119</v>
+        <v>46121</v>
       </c>
       <c r="G31" s="28" t="s">
-        <v>202</v>
+        <v>204</v>
       </c>
       <c r="H31" s="28" t="s">
         <v>205</v>
@@ -9010,6 +9010,27 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
+    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
+      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    </lcf76f155ced4ddcb4097134ff3c332f>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100A92AB09DCDF6014AA0D6826BF29E2C8E" ma:contentTypeVersion="19" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="58b13f75919cba2dcad85f84b1d5db00">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="1e76d14e-d0ce-457c-8343-9b55836d9ead" xmlns:ns3="a56712a3-8dfd-4688-917a-22f0cf513b89" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="a3b16ea44285e6579c272a3325f660d0" ns2:_="" ns3:_="">
     <xsd:import namespace="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
@@ -9273,42 +9294,10 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement>
-    <TaxCatchAll xmlns="a56712a3-8dfd-4688-917a-22f0cf513b89" xsi:nil="true"/>
-    <UserStoryALM xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead" xsi:nil="true"/>
-    <lcf76f155ced4ddcb4097134ff3c332f xmlns="1e76d14e-d0ce-457c-8343-9b55836d9ead">
-      <Terms xmlns="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    </lcf76f155ced4ddcb4097134ff3c332f>
-  </documentManagement>
-</p:properties>
-</file>
-
-<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
-    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
-    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
-    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
-    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
@@ -9331,9 +9320,20 @@
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{9413B232-C823-4C2A-B920-858F3EB4F277}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{1AD72871-87C6-44C4-AEDE-C35BE2C233EE}">
   <ds:schemaRefs>
-    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="1e76d14e-d0ce-457c-8343-9b55836d9ead"/>
+    <ds:schemaRef ds:uri="a56712a3-8dfd-4688-917a-22f0cf513b89"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
 </file>
